--- a/out/MLP-S4_repeat_2_000007.xlsx
+++ b/out/MLP-S4_repeat_2_000007.xlsx
@@ -2534,7 +2534,7 @@
         <v>0</v>
       </c>
       <c r="JB2" t="n">
-        <v>-0.9291019071641193</v>
+        <v>-1.623677129033441</v>
       </c>
       <c r="JC2" t="n">
         <v>0</v>
@@ -3329,7 +3329,7 @@
         <v>0</v>
       </c>
       <c r="JB3" t="n">
-        <v>-0.9291019071641193</v>
+        <v>-1.623677129033441</v>
       </c>
       <c r="JC3" t="n">
         <v>0</v>
@@ -4124,7 +4124,7 @@
         <v>0</v>
       </c>
       <c r="JB4" t="n">
-        <v>-0.9291019071641193</v>
+        <v>-1.623677129033441</v>
       </c>
       <c r="JC4" t="n">
         <v>0</v>
@@ -4912,14 +4912,14 @@
       </c>
       <c r="IZ5" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB5" t="n">
-        <v>3.415552302146114</v>
+        <v>-1.623677129033441</v>
       </c>
       <c r="JC5" t="n">
         <v>0</v>
@@ -5714,7 +5714,7 @@
         <v>0</v>
       </c>
       <c r="JB6" t="n">
-        <v>-0.3291019071641194</v>
+        <v>-1.623677129033441</v>
       </c>
       <c r="JC6" t="n">
         <v>0</v>
@@ -6509,7 +6509,7 @@
         <v>0</v>
       </c>
       <c r="JB7" t="n">
-        <v>-0.3291019071641194</v>
+        <v>-1.623677129033441</v>
       </c>
       <c r="JC7" t="n">
         <v>0</v>
@@ -7304,7 +7304,7 @@
         <v>0</v>
       </c>
       <c r="JB8" t="n">
-        <v>-0.9291019071641193</v>
+        <v>-1.623677129033441</v>
       </c>
       <c r="JC8" t="n">
         <v>0</v>
@@ -8099,7 +8099,7 @@
         <v>0</v>
       </c>
       <c r="JB9" t="n">
-        <v>-0.9291019071641193</v>
+        <v>-1.623677129033441</v>
       </c>
       <c r="JC9" t="n">
         <v>0</v>
@@ -8891,10 +8891,10 @@
         </is>
       </c>
       <c r="JA10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB10" t="n">
-        <v>-0.9291019071641193</v>
+        <v>1.180723568071307</v>
       </c>
       <c r="JC10" t="n">
         <v>0</v>
@@ -9689,7 +9689,7 @@
         <v>0</v>
       </c>
       <c r="JB11" t="n">
-        <v>-0.9291019071641193</v>
+        <v>-1.023677129033441</v>
       </c>
       <c r="JC11" t="n">
         <v>0</v>
@@ -10484,7 +10484,7 @@
         <v>0</v>
       </c>
       <c r="JB12" t="n">
-        <v>-0.9291019071641193</v>
+        <v>-1.023677129033441</v>
       </c>
       <c r="JC12" t="n">
         <v>0</v>
@@ -11279,7 +11279,7 @@
         <v>0</v>
       </c>
       <c r="JB13" t="n">
-        <v>-0.9291019071641193</v>
+        <v>-1.623677129033441</v>
       </c>
       <c r="JC13" t="n">
         <v>0</v>
@@ -12071,10 +12071,10 @@
         </is>
       </c>
       <c r="JA14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB14" t="n">
-        <v>-0.9291019071641193</v>
+        <v>1.780723568071307</v>
       </c>
       <c r="JC14" t="n">
         <v>0</v>
@@ -12869,7 +12869,7 @@
         <v>0</v>
       </c>
       <c r="JB15" t="n">
-        <v>-0.9291019071641193</v>
+        <v>-1.023677129033441</v>
       </c>
       <c r="JC15" t="n">
         <v>0</v>
@@ -13664,7 +13664,7 @@
         <v>0</v>
       </c>
       <c r="JB16" t="n">
-        <v>-0.9291019071641193</v>
+        <v>-1.023677129033441</v>
       </c>
       <c r="JC16" t="n">
         <v>0</v>
@@ -14459,7 +14459,7 @@
         <v>0</v>
       </c>
       <c r="JB17" t="n">
-        <v>-0.9291019071641193</v>
+        <v>-1.623677129033441</v>
       </c>
       <c r="JC17" t="n">
         <v>0</v>
@@ -15251,10 +15251,10 @@
         </is>
       </c>
       <c r="JA18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB18" t="n">
-        <v>-0.9291019071641193</v>
+        <v>1.780723568071307</v>
       </c>
       <c r="JC18" t="n">
         <v>0</v>
@@ -16049,7 +16049,7 @@
         <v>0</v>
       </c>
       <c r="JB19" t="n">
-        <v>-0.9291019071641193</v>
+        <v>-1.023677129033441</v>
       </c>
       <c r="JC19" t="n">
         <v>0</v>
@@ -16844,7 +16844,7 @@
         <v>0</v>
       </c>
       <c r="JB20" t="n">
-        <v>-0.9291019071641193</v>
+        <v>-1.023677129033441</v>
       </c>
       <c r="JC20" t="n">
         <v>0</v>
@@ -17636,10 +17636,10 @@
         </is>
       </c>
       <c r="JA21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB21" t="n">
-        <v>-0.9291019071641193</v>
+        <v>1.780723568071307</v>
       </c>
       <c r="JC21" t="n">
         <v>0</v>
@@ -18431,10 +18431,10 @@
         </is>
       </c>
       <c r="JA22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB22" t="n">
-        <v>-0.9291019071641193</v>
+        <v>1.780723568071307</v>
       </c>
       <c r="JC22" t="n">
         <v>0</v>
@@ -19229,7 +19229,7 @@
         <v>1</v>
       </c>
       <c r="JB23" t="n">
-        <v>3.415552302146114</v>
+        <v>1.780723568071307</v>
       </c>
       <c r="JC23" t="n">
         <v>0</v>
@@ -20021,10 +20021,10 @@
         </is>
       </c>
       <c r="JA24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB24" t="n">
-        <v>-0.3291019071641194</v>
+        <v>1.780723568071307</v>
       </c>
       <c r="JC24" t="n">
         <v>0</v>
@@ -20816,10 +20816,10 @@
         </is>
       </c>
       <c r="JA25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB25" t="n">
-        <v>-0.3291019071641194</v>
+        <v>1.780723568071307</v>
       </c>
       <c r="JC25" t="n">
         <v>0</v>
@@ -21611,10 +21611,10 @@
         </is>
       </c>
       <c r="JA26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB26" t="n">
-        <v>-0.9291019071641193</v>
+        <v>1.780723568071307</v>
       </c>
       <c r="JC26" t="n">
         <v>0</v>
@@ -22406,10 +22406,10 @@
         </is>
       </c>
       <c r="JA27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB27" t="n">
-        <v>-0.9291019071641193</v>
+        <v>1.780723568071307</v>
       </c>
       <c r="JC27" t="n">
         <v>0</v>
@@ -23201,10 +23201,10 @@
         </is>
       </c>
       <c r="JA28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB28" t="n">
-        <v>-0.9291019071641193</v>
+        <v>1.780723568071307</v>
       </c>
       <c r="JC28" t="n">
         <v>0</v>
@@ -23996,10 +23996,10 @@
         </is>
       </c>
       <c r="JA29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB29" t="n">
-        <v>-0.9291019071641193</v>
+        <v>1.780723568071307</v>
       </c>
       <c r="JC29" t="n">
         <v>0</v>
@@ -24791,10 +24791,10 @@
         </is>
       </c>
       <c r="JA30" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB30" t="n">
-        <v>-0.9291019071641193</v>
+        <v>1.180723568071307</v>
       </c>
       <c r="JC30" t="n">
         <v>0</v>
@@ -25586,10 +25586,10 @@
         </is>
       </c>
       <c r="JA31" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB31" t="n">
-        <v>-0.9291019071641193</v>
+        <v>1.180723568071307</v>
       </c>
       <c r="JC31" t="n">
         <v>0</v>
@@ -26381,10 +26381,10 @@
         </is>
       </c>
       <c r="JA32" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB32" t="n">
-        <v>-0.9291019071641193</v>
+        <v>1.180723568071307</v>
       </c>
       <c r="JC32" t="n">
         <v>0</v>
@@ -27172,14 +27172,14 @@
       </c>
       <c r="IZ33" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA33" t="n">
         <v>0</v>
       </c>
       <c r="JB33" t="n">
-        <v>-0.9291019071641193</v>
+        <v>-1.623677129033441</v>
       </c>
       <c r="JC33" t="n">
         <v>0</v>
@@ -27971,10 +27971,10 @@
         </is>
       </c>
       <c r="JA34" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB34" t="n">
-        <v>-0.9291019071641193</v>
+        <v>1.180723568071307</v>
       </c>
       <c r="JC34" t="n">
         <v>0</v>
@@ -28766,10 +28766,10 @@
         </is>
       </c>
       <c r="JA35" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB35" t="n">
-        <v>-0.9291019071641193</v>
+        <v>1.180723568071307</v>
       </c>
       <c r="JC35" t="n">
         <v>0</v>
@@ -29564,7 +29564,7 @@
         <v>1</v>
       </c>
       <c r="JB36" t="n">
-        <v>3.415552302146114</v>
+        <v>1.780723568071307</v>
       </c>
       <c r="JC36" t="n">
         <v>0</v>
@@ -30359,7 +30359,7 @@
         <v>1</v>
       </c>
       <c r="JB37" t="n">
-        <v>3.415552302146114</v>
+        <v>1.780723568071307</v>
       </c>
       <c r="JC37" t="n">
         <v>0</v>
@@ -31154,7 +31154,7 @@
         <v>1</v>
       </c>
       <c r="JB38" t="n">
-        <v>3.415552302146114</v>
+        <v>1.780723568071307</v>
       </c>
       <c r="JC38" t="n">
         <v>0</v>
@@ -31949,10 +31949,10 @@
         <v>1</v>
       </c>
       <c r="JB39" t="n">
-        <v>3.415552302146114</v>
+        <v>1.780723568071307</v>
       </c>
       <c r="JC39" t="n">
-        <v>-0.0003604635853798827</v>
+        <v>-0.0002357946269055828</v>
       </c>
     </row>
     <row r="40">
@@ -32733,7 +32733,7 @@
         <v>0</v>
       </c>
       <c r="IY40" t="n">
-        <v>4.155612693188337</v>
+        <v>2.718363726226739</v>
       </c>
       <c r="IZ40" t="inlineStr">
         <is>
@@ -32744,10 +32744,10 @@
         <v>1</v>
       </c>
       <c r="JB40" t="n">
-        <v>3.415552302146114</v>
+        <v>1.780723568071307</v>
       </c>
       <c r="JC40" t="n">
-        <v>8.317649365197576</v>
+        <v>5.440929703749978</v>
       </c>
     </row>
     <row r="41">
@@ -33528,7 +33528,7 @@
         <v>0</v>
       </c>
       <c r="IY41" t="n">
-        <v>0.6231526832897226</v>
+        <v>0.4076307894486836</v>
       </c>
       <c r="IZ41" t="inlineStr">
         <is>
@@ -33539,10 +33539,10 @@
         <v>1</v>
       </c>
       <c r="JB41" t="n">
-        <v>3.415552302146114</v>
+        <v>1.780723568071307</v>
       </c>
       <c r="JC41" t="n">
-        <v>5.402764483231868</v>
+        <v>3.534178986871036</v>
       </c>
     </row>
     <row r="42">
@@ -34323,7 +34323,7 @@
         <v>0</v>
       </c>
       <c r="IY42" t="n">
-        <v>0.7791436148826281</v>
+        <v>0.5096711212921849</v>
       </c>
       <c r="IZ42" t="inlineStr">
         <is>
@@ -34334,10 +34334,10 @@
         <v>1</v>
       </c>
       <c r="JB42" t="n">
-        <v>3.415552302146114</v>
+        <v>1.780723568071307</v>
       </c>
       <c r="JC42" t="n">
-        <v>6.337997990699301</v>
+        <v>4.145955174618856</v>
       </c>
     </row>
     <row r="43">
@@ -35118,7 +35118,7 @@
         <v>0</v>
       </c>
       <c r="IY43" t="n">
-        <v>1.116898676922276</v>
+        <v>0.7306111353071767</v>
       </c>
       <c r="IZ43" t="inlineStr">
         <is>
@@ -35129,10 +35129,10 @@
         <v>1</v>
       </c>
       <c r="JB43" t="n">
-        <v>3.415552302146114</v>
+        <v>1.180723568071307</v>
       </c>
       <c r="JC43" t="n">
-        <v>7.793091434888637</v>
+        <v>5.09779395391323</v>
       </c>
     </row>
     <row r="44">
@@ -35913,7 +35913,7 @@
         <v>0</v>
       </c>
       <c r="IY44" t="n">
-        <v>1.194860349256982</v>
+        <v>0.781608847422153</v>
       </c>
       <c r="IZ44" t="inlineStr">
         <is>
@@ -35924,10 +35924,10 @@
         <v>1</v>
       </c>
       <c r="JB44" t="n">
-        <v>3.415552302146114</v>
+        <v>1.180723568071307</v>
       </c>
       <c r="JC44" t="n">
-        <v>9.06599673043802</v>
+        <v>5.930455683155816</v>
       </c>
     </row>
     <row r="45">
@@ -36708,7 +36708,7 @@
         <v>0</v>
       </c>
       <c r="IY45" t="n">
-        <v>1.266311134954735</v>
+        <v>0.8283478377078007</v>
       </c>
       <c r="IZ45" t="inlineStr">
         <is>
@@ -36719,10 +36719,10 @@
         <v>1</v>
       </c>
       <c r="JB45" t="n">
-        <v>2.815552302146114</v>
+        <v>1.180723568071307</v>
       </c>
       <c r="JC45" t="n">
-        <v>10.40384906616079</v>
+        <v>6.805602436027013</v>
       </c>
     </row>
     <row r="46">
@@ -37503,7 +37503,7 @@
         <v>0</v>
       </c>
       <c r="IY46" t="n">
-        <v>0.5714619975069256</v>
+        <v>0.3738179729027461</v>
       </c>
       <c r="IZ46" t="inlineStr">
         <is>
@@ -37514,10 +37514,10 @@
         <v>1</v>
       </c>
       <c r="JB46" t="n">
-        <v>2.815552302146114</v>
+        <v>1.180723568071307</v>
       </c>
       <c r="JC46" t="n">
-        <v>10.27941095943332</v>
+        <v>6.724202046378685</v>
       </c>
     </row>
     <row r="47">
@@ -38298,7 +38298,7 @@
         <v>0</v>
       </c>
       <c r="IY47" t="n">
-        <v>0.2759900252444427</v>
+        <v>0.1805369949854015</v>
       </c>
       <c r="IZ47" t="inlineStr">
         <is>
@@ -38306,13 +38306,13 @@
         </is>
       </c>
       <c r="JA47" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB47" t="n">
-        <v>2.815552302146114</v>
+        <v>-1.623677129033441</v>
       </c>
       <c r="JC47" t="n">
-        <v>10.25948086265405</v>
+        <v>6.711164893607577</v>
       </c>
     </row>
     <row r="48">
@@ -39093,7 +39093,7 @@
         <v>0</v>
       </c>
       <c r="IY48" t="n">
-        <v>0.1315016431784234</v>
+        <v>0.08602111607760177</v>
       </c>
       <c r="IZ48" t="inlineStr">
         <is>
@@ -39101,13 +39101,13 @@
         </is>
       </c>
       <c r="JA48" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB48" t="n">
-        <v>2.815552302146114</v>
+        <v>-1.623677129033441</v>
       </c>
       <c r="JC48" t="n">
-        <v>10.24627366207712</v>
+        <v>6.70252547202752</v>
       </c>
     </row>
     <row r="49">
@@ -39888,7 +39888,7 @@
         <v>0</v>
       </c>
       <c r="IY49" t="n">
-        <v>0.03896265639495582</v>
+        <v>0.02548745665628013</v>
       </c>
       <c r="IZ49" t="inlineStr">
         <is>
@@ -39896,13 +39896,13 @@
         </is>
       </c>
       <c r="JA49" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB49" t="n">
-        <v>-0.9291019071641193</v>
+        <v>1.180723568071307</v>
       </c>
       <c r="JC49" t="n">
-        <v>10.19255798453488</v>
+        <v>6.66738764052103</v>
       </c>
     </row>
     <row r="50">
@@ -40683,7 +40683,7 @@
         <v>0</v>
       </c>
       <c r="IY50" t="n">
-        <v>0.02577282474534589</v>
+        <v>0.01685900213767146</v>
       </c>
       <c r="IZ50" t="inlineStr">
         <is>
@@ -40691,13 +40691,13 @@
         </is>
       </c>
       <c r="JA50" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB50" t="n">
-        <v>-0.9291019071641193</v>
+        <v>1.180723568071307</v>
       </c>
       <c r="JC50" t="n">
-        <v>10.20511990686067</v>
+        <v>6.67560488009164</v>
       </c>
     </row>
     <row r="51">
@@ -41478,7 +41478,7 @@
         <v>0</v>
       </c>
       <c r="IY51" t="n">
-        <v>0.01318983812480389</v>
+        <v>0.008626254290140174</v>
       </c>
       <c r="IZ51" t="inlineStr">
         <is>
@@ -41489,10 +41489,10 @@
         <v>0</v>
       </c>
       <c r="JB51" t="n">
-        <v>-0.9291019071641193</v>
+        <v>-1.623677129033441</v>
       </c>
       <c r="JC51" t="n">
-        <v>10.20570857652375</v>
+        <v>6.675988222394737</v>
       </c>
     </row>
     <row r="52">
@@ -42273,7 +42273,7 @@
         <v>0</v>
       </c>
       <c r="IY52" t="n">
-        <v>0.006744669631670948</v>
+        <v>0.004410220134900639</v>
       </c>
       <c r="IZ52" t="inlineStr">
         <is>
@@ -42284,10 +42284,10 @@
         <v>0</v>
       </c>
       <c r="JB52" t="n">
-        <v>-0.9291019071641193</v>
+        <v>-1.623677129033441</v>
       </c>
       <c r="JC52" t="n">
-        <v>10.2060002284351</v>
+        <v>6.676177273891111</v>
       </c>
     </row>
     <row r="53">
@@ -43068,7 +43068,7 @@
         <v>0</v>
       </c>
       <c r="IY53" t="n">
-        <v>0.00253207824239737</v>
+        <v>0.001654848623382289</v>
       </c>
       <c r="IZ53" t="inlineStr">
         <is>
@@ -43079,10 +43079,10 @@
         <v>0</v>
       </c>
       <c r="JB53" t="n">
-        <v>-0.9291019071641193</v>
+        <v>-1.623677129033441</v>
       </c>
       <c r="JC53" t="n">
-        <v>10.2043153590409</v>
+        <v>6.6750734060027</v>
       </c>
     </row>
     <row r="54">
@@ -43863,7 +43863,7 @@
         <v>0</v>
       </c>
       <c r="IY54" t="n">
-        <v>0.001377710017885418</v>
+        <v>0.0008992065510754283</v>
       </c>
       <c r="IZ54" t="inlineStr">
         <is>
@@ -43874,10 +43874,10 @@
         <v>0</v>
       </c>
       <c r="JB54" t="n">
-        <v>-0.9291019071641193</v>
+        <v>-1.623677129033441</v>
       </c>
       <c r="JC54" t="n">
-        <v>10.20453735570176</v>
+        <v>6.675216871335629</v>
       </c>
     </row>
     <row r="55">
@@ -44658,7 +44658,7 @@
         <v>0</v>
       </c>
       <c r="IY55" t="n">
-        <v>0.0006609836985678793</v>
+        <v>0.000430512012905964</v>
       </c>
       <c r="IZ55" t="inlineStr">
         <is>
@@ -44666,13 +44666,13 @@
         </is>
       </c>
       <c r="JA55" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB55" t="n">
-        <v>-0.9291019071641193</v>
+        <v>1.180723568071307</v>
       </c>
       <c r="JC55" t="n">
-        <v>10.20448070844907</v>
+        <v>6.67517808674724</v>
       </c>
     </row>
     <row r="56">
@@ -45453,7 +45453,7 @@
         <v>0</v>
       </c>
       <c r="IY56" t="n">
-        <v>0.0004072771942052819</v>
+        <v>0.000264603702177201</v>
       </c>
       <c r="IZ56" t="inlineStr">
         <is>
@@ -45461,13 +45461,13 @@
         </is>
       </c>
       <c r="JA56" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB56" t="n">
-        <v>-0.9291019071641193</v>
+        <v>1.780723568071307</v>
       </c>
       <c r="JC56" t="n">
-        <v>10.20463415717052</v>
+        <v>6.675276767941257</v>
       </c>
     </row>
     <row r="57">
@@ -46248,7 +46248,7 @@
         <v>0</v>
       </c>
       <c r="IY57" t="n">
-        <v>0.0002111675230719449</v>
+        <v>0.0001360235745755069</v>
       </c>
       <c r="IZ57" t="inlineStr">
         <is>
@@ -46259,10 +46259,10 @@
         <v>0</v>
       </c>
       <c r="JB57" t="n">
-        <v>-0.9291019071641193</v>
+        <v>-1.023677129033441</v>
       </c>
       <c r="JC57" t="n">
-        <v>10.2046479909593</v>
+        <v>6.675284100214915</v>
       </c>
     </row>
     <row r="58">
@@ -47043,7 +47043,7 @@
         <v>0</v>
       </c>
       <c r="IY58" t="n">
-        <v>9.990477873244368e-05</v>
+        <v>6.393742602417726e-05</v>
       </c>
       <c r="IZ58" t="inlineStr">
         <is>
@@ -47054,10 +47054,10 @@
         <v>1</v>
       </c>
       <c r="JB58" t="n">
-        <v>3.415552302146114</v>
+        <v>1.780723568071307</v>
       </c>
       <c r="JC58" t="n">
-        <v>10.20463649766222</v>
+        <v>6.675274833191119</v>
       </c>
     </row>
     <row r="59">
@@ -47838,7 +47838,7 @@
         <v>0</v>
       </c>
       <c r="IY59" t="n">
-        <v>6.151561164366101e-05</v>
+        <v>3.849097684393219e-05</v>
       </c>
       <c r="IZ59" t="inlineStr">
         <is>
@@ -47846,13 +47846,13 @@
         </is>
       </c>
       <c r="JA59" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB59" t="n">
-        <v>3.415552302146114</v>
+        <v>-1.623677129033441</v>
       </c>
       <c r="JC59" t="n">
-        <v>10.20466085784762</v>
+        <v>6.6752891272934</v>
       </c>
     </row>
     <row r="60">
@@ -48633,7 +48633,7 @@
         <v>0</v>
       </c>
       <c r="IY60" t="n">
-        <v>2.530589321855379e-05</v>
+        <v>1.481539171982363e-05</v>
       </c>
       <c r="IZ60" t="inlineStr">
         <is>
@@ -48644,10 +48644,10 @@
         <v>0</v>
       </c>
       <c r="JB60" t="n">
-        <v>-0.3291019071641194</v>
+        <v>-1.023677129033441</v>
       </c>
       <c r="JC60" t="n">
-        <v>10.20464979643704</v>
+        <v>6.675280124715577</v>
       </c>
     </row>
     <row r="61">
@@ -49428,7 +49428,7 @@
         <v>0</v>
       </c>
       <c r="IY61" t="n">
-        <v>8.38179904731087e-06</v>
+        <v>4.264322417369065e-06</v>
       </c>
       <c r="IZ61" t="inlineStr">
         <is>
@@ -49436,13 +49436,13 @@
         </is>
       </c>
       <c r="JA61" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB61" t="n">
-        <v>-0.3291019071641194</v>
+        <v>1.180723568071307</v>
       </c>
       <c r="JC61" t="n">
-        <v>10.2046410971978</v>
+        <v>6.675272658138582</v>
       </c>
     </row>
     <row r="62">
@@ -50223,7 +50223,7 @@
         <v>0</v>
       </c>
       <c r="IY62" t="n">
-        <v>2.788397616378431e-06</v>
+        <v>-5.494870763551826e-07</v>
       </c>
       <c r="IZ62" t="inlineStr">
         <is>
@@ -50234,10 +50234,10 @@
         <v>0</v>
       </c>
       <c r="JB62" t="n">
-        <v>-0.9291019071641193</v>
+        <v>-1.623677129033441</v>
       </c>
       <c r="JC62" t="n">
-        <v>10.20463725475757</v>
+        <v>6.675268402960413</v>
       </c>
     </row>
     <row r="63">
@@ -51018,7 +51018,7 @@
         <v>0</v>
       </c>
       <c r="IY63" t="n">
-        <v>-2.093548687745288e-06</v>
+        <v>-3.062365791830193e-06</v>
       </c>
       <c r="IZ63" t="inlineStr">
         <is>
@@ -51029,10 +51029,10 @@
         <v>0</v>
       </c>
       <c r="JB63" t="n">
-        <v>-0.9291019071641193</v>
+        <v>-1.623677129033441</v>
       </c>
       <c r="JC63" t="n">
-        <v>10.20463124333098</v>
+        <v>6.675262680681382</v>
       </c>
     </row>
     <row r="64">
@@ -51813,7 +51813,7 @@
         <v>0</v>
       </c>
       <c r="IY64" t="n">
-        <v>-3.107779831880603e-06</v>
+        <v>-4.053889915940302e-06</v>
       </c>
       <c r="IZ64" t="inlineStr">
         <is>
@@ -51821,13 +51821,13 @@
         </is>
       </c>
       <c r="JA64" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB64" t="n">
-        <v>-0.9291019071641193</v>
+        <v>1.180723568071307</v>
       </c>
       <c r="JC64" t="n">
-        <v>10.20462615008884</v>
+        <v>6.675257611326013</v>
       </c>
     </row>
     <row r="65">
@@ -52619,10 +52619,10 @@
         <v>1</v>
       </c>
       <c r="JB65" t="n">
-        <v>3.415552302146114</v>
+        <v>1.780723568071307</v>
       </c>
       <c r="JC65" t="n">
-        <v>10.20462178511487</v>
+        <v>6.675253246352044</v>
       </c>
     </row>
     <row r="66">
@@ -53414,10 +53414,10 @@
         <v>1</v>
       </c>
       <c r="JB66" t="n">
-        <v>3.415552302146114</v>
+        <v>1.780723568071307</v>
       </c>
       <c r="JC66" t="n">
-        <v>10.20462287636133</v>
+        <v>6.675254337598501</v>
       </c>
     </row>
     <row r="67">
@@ -54206,13 +54206,13 @@
         </is>
       </c>
       <c r="JA67" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB67" t="n">
-        <v>3.415552302146114</v>
+        <v>-1.023677129033441</v>
       </c>
       <c r="JC67" t="n">
-        <v>10.20462218675419</v>
+        <v>6.675253647991365</v>
       </c>
     </row>
     <row r="68">
@@ -55004,10 +55004,10 @@
         <v>0</v>
       </c>
       <c r="JB68" t="n">
-        <v>-0.3291019071641194</v>
+        <v>-1.623677129033441</v>
       </c>
       <c r="JC68" t="n">
-        <v>10.20462221706659</v>
+        <v>6.675253678303767</v>
       </c>
     </row>
     <row r="69">
@@ -55796,13 +55796,13 @@
         </is>
       </c>
       <c r="JA69" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB69" t="n">
-        <v>-0.3291019071641194</v>
+        <v>1.180723568071307</v>
       </c>
       <c r="JC69" t="n">
-        <v>10.20462202761409</v>
+        <v>6.675253488851257</v>
       </c>
     </row>
     <row r="70">
@@ -56591,13 +56591,13 @@
         </is>
       </c>
       <c r="JA70" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB70" t="n">
-        <v>-0.9291019071641193</v>
+        <v>1.780723568071307</v>
       </c>
       <c r="JC70" t="n">
-        <v>10.20462208066079</v>
+        <v>6.67525354189796</v>
       </c>
     </row>
     <row r="71">
@@ -57389,10 +57389,10 @@
         <v>0</v>
       </c>
       <c r="JB71" t="n">
-        <v>-0.9291019071641193</v>
+        <v>-1.023677129033441</v>
       </c>
       <c r="JC71" t="n">
-        <v>10.20462213370749</v>
+        <v>6.675253594944662</v>
       </c>
     </row>
     <row r="72">
@@ -58184,10 +58184,10 @@
         <v>0</v>
       </c>
       <c r="JB72" t="n">
-        <v>-0.9291019071641193</v>
+        <v>-1.623677129033441</v>
       </c>
       <c r="JC72" t="n">
-        <v>10.20462209581699</v>
+        <v>6.67525355705416</v>
       </c>
     </row>
     <row r="73">
@@ -58979,10 +58979,10 @@
         <v>0</v>
       </c>
       <c r="JB73" t="n">
-        <v>-0.9291019071641193</v>
+        <v>-1.623677129033441</v>
       </c>
       <c r="JC73" t="n">
-        <v>10.20462196698928</v>
+        <v>6.675253428226453</v>
       </c>
     </row>
     <row r="74">
@@ -59774,10 +59774,10 @@
         <v>0</v>
       </c>
       <c r="JB74" t="n">
-        <v>-0.9291019071641193</v>
+        <v>-1.623677129033441</v>
       </c>
       <c r="JC74" t="n">
-        <v>10.20462182300538</v>
+        <v>6.675253284242546</v>
       </c>
     </row>
     <row r="75">
@@ -60569,10 +60569,10 @@
         <v>0</v>
       </c>
       <c r="JB75" t="n">
-        <v>-0.9291019071641193</v>
+        <v>-1.623677129033441</v>
       </c>
       <c r="JC75" t="n">
-        <v>10.20462166386527</v>
+        <v>6.675253125102438</v>
       </c>
     </row>
     <row r="76">
@@ -61364,10 +61364,10 @@
         <v>0</v>
       </c>
       <c r="JB76" t="n">
-        <v>-0.9291019071641193</v>
+        <v>-1.623677129033441</v>
       </c>
       <c r="JC76" t="n">
-        <v>10.20462171691197</v>
+        <v>6.67525317814914</v>
       </c>
     </row>
     <row r="77">
@@ -62156,13 +62156,13 @@
         </is>
       </c>
       <c r="JA77" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB77" t="n">
-        <v>-0.9291019071641193</v>
+        <v>1.780723568071307</v>
       </c>
       <c r="JC77" t="n">
-        <v>10.20462166386527</v>
+        <v>6.675253125102438</v>
       </c>
     </row>
     <row r="78">
@@ -62954,10 +62954,10 @@
         <v>0</v>
       </c>
       <c r="JB78" t="n">
-        <v>-0.9291019071641193</v>
+        <v>-1.023677129033441</v>
       </c>
       <c r="JC78" t="n">
-        <v>10.20462166386527</v>
+        <v>6.675253125102438</v>
       </c>
     </row>
     <row r="79">
@@ -63746,13 +63746,13 @@
         </is>
       </c>
       <c r="JA79" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB79" t="n">
-        <v>-0.9291019071641193</v>
+        <v>1.780723568071307</v>
       </c>
       <c r="JC79" t="n">
-        <v>10.20462148199086</v>
+        <v>6.675252943228029</v>
       </c>
     </row>
     <row r="80">
@@ -64541,13 +64541,13 @@
         </is>
       </c>
       <c r="JA80" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB80" t="n">
-        <v>-0.9291019071641193</v>
+        <v>1.780723568071307</v>
       </c>
       <c r="JC80" t="n">
-        <v>10.20462164870907</v>
+        <v>6.675253109946237</v>
       </c>
     </row>
     <row r="81">
@@ -65339,10 +65339,10 @@
         <v>0</v>
       </c>
       <c r="JB81" t="n">
-        <v>-0.9291019071641193</v>
+        <v>-1.023677129033441</v>
       </c>
       <c r="JC81" t="n">
-        <v>10.20462184573968</v>
+        <v>6.675253306976847</v>
       </c>
     </row>
     <row r="82">
@@ -66134,10 +66134,10 @@
         <v>0</v>
       </c>
       <c r="JB82" t="n">
-        <v>-0.9291019071641193</v>
+        <v>-1.023677129033441</v>
       </c>
       <c r="JC82" t="n">
-        <v>10.20462168659957</v>
+        <v>6.675253147836739</v>
       </c>
     </row>
     <row r="83">
@@ -66926,13 +66926,13 @@
         </is>
       </c>
       <c r="JA83" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB83" t="n">
-        <v>-0.9291019071641193</v>
+        <v>1.180723568071307</v>
       </c>
       <c r="JC83" t="n">
-        <v>10.20462172449007</v>
+        <v>6.67525318572724</v>
       </c>
     </row>
     <row r="84">
@@ -67724,10 +67724,10 @@
         <v>0</v>
       </c>
       <c r="JB84" t="n">
-        <v>-0.9291019071641193</v>
+        <v>-1.623677129033441</v>
       </c>
       <c r="JC84" t="n">
-        <v>10.20462192152068</v>
+        <v>6.675253382757851</v>
       </c>
     </row>
     <row r="85">
@@ -68519,10 +68519,10 @@
         <v>0</v>
       </c>
       <c r="JB85" t="n">
-        <v>-0.9291019071641193</v>
+        <v>-1.623677129033441</v>
       </c>
       <c r="JC85" t="n">
-        <v>10.20462189878638</v>
+        <v>6.67525336002355</v>
       </c>
     </row>
     <row r="86">
@@ -69314,10 +69314,10 @@
         <v>0</v>
       </c>
       <c r="JB86" t="n">
-        <v>-0.9291019071641193</v>
+        <v>-1.623677129033441</v>
       </c>
       <c r="JC86" t="n">
-        <v>10.20462174722437</v>
+        <v>6.675253208461542</v>
       </c>
     </row>
     <row r="87">
@@ -70106,13 +70106,13 @@
         </is>
       </c>
       <c r="JA87" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB87" t="n">
-        <v>-0.9291019071641193</v>
+        <v>1.180723568071307</v>
       </c>
       <c r="JC87" t="n">
-        <v>10.20462167144337</v>
+        <v>6.675253132680538</v>
       </c>
     </row>
     <row r="88">
@@ -70904,10 +70904,10 @@
         <v>0</v>
       </c>
       <c r="JB88" t="n">
-        <v>-0.9291019071641193</v>
+        <v>-1.623677129033441</v>
       </c>
       <c r="JC88" t="n">
-        <v>10.20462176995867</v>
+        <v>6.675253231195843</v>
       </c>
     </row>
     <row r="89">
@@ -71696,13 +71696,13 @@
         </is>
       </c>
       <c r="JA89" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB89" t="n">
-        <v>-0.9291019071641193</v>
+        <v>1.780723568071307</v>
       </c>
       <c r="JC89" t="n">
-        <v>10.20462177753677</v>
+        <v>6.675253238773944</v>
       </c>
     </row>
     <row r="90">
@@ -72494,10 +72494,10 @@
         <v>0</v>
       </c>
       <c r="JB90" t="n">
-        <v>-0.9291019071641193</v>
+        <v>-1.023677129033441</v>
       </c>
       <c r="JC90" t="n">
-        <v>10.20462204277029</v>
+        <v>6.675253504007458</v>
       </c>
     </row>
     <row r="91">
@@ -73286,13 +73286,13 @@
         </is>
       </c>
       <c r="JA91" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB91" t="n">
-        <v>-0.9291019071641193</v>
+        <v>1.780723568071307</v>
       </c>
       <c r="JC91" t="n">
-        <v>10.20462174722437</v>
+        <v>6.675253208461542</v>
       </c>
     </row>
     <row r="92">
@@ -74081,13 +74081,13 @@
         </is>
       </c>
       <c r="JA92" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB92" t="n">
-        <v>-0.9291019071641193</v>
+        <v>1.780723568071307</v>
       </c>
       <c r="JC92" t="n">
-        <v>10.20462198972358</v>
+        <v>6.675253450960755</v>
       </c>
     </row>
     <row r="93">
@@ -74879,10 +74879,10 @@
         <v>0</v>
       </c>
       <c r="JB93" t="n">
-        <v>-0.9291019071641193</v>
+        <v>-1.023677129033441</v>
       </c>
       <c r="JC93" t="n">
-        <v>10.20462207308269</v>
+        <v>6.675253534319859</v>
       </c>
     </row>
     <row r="94">
@@ -75674,10 +75674,10 @@
         <v>1</v>
       </c>
       <c r="JB94" t="n">
-        <v>3.415552302146114</v>
+        <v>1.780723568071307</v>
       </c>
       <c r="JC94" t="n">
-        <v>10.20462190636448</v>
+        <v>6.675253367601651</v>
       </c>
     </row>
     <row r="95">
@@ -76469,10 +76469,10 @@
         <v>0</v>
       </c>
       <c r="JB95" t="n">
-        <v>-0.3291019071641194</v>
+        <v>-1.623677129033441</v>
       </c>
       <c r="JC95" t="n">
-        <v>10.20462209581699</v>
+        <v>6.67525355705416</v>
       </c>
     </row>
     <row r="96">
@@ -77264,10 +77264,10 @@
         <v>0</v>
       </c>
       <c r="JB96" t="n">
-        <v>-0.3291019071641194</v>
+        <v>-1.623677129033441</v>
       </c>
       <c r="JC96" t="n">
-        <v>10.20462174722437</v>
+        <v>6.675253208461542</v>
       </c>
     </row>
     <row r="97">
@@ -78059,10 +78059,10 @@
         <v>0</v>
       </c>
       <c r="JB97" t="n">
-        <v>-0.9291019071641193</v>
+        <v>-1.623677129033441</v>
       </c>
       <c r="JC97" t="n">
-        <v>10.20462154261566</v>
+        <v>6.675253003852831</v>
       </c>
     </row>
     <row r="98">
@@ -78854,10 +78854,10 @@
         <v>0</v>
       </c>
       <c r="JB98" t="n">
-        <v>-0.9291019071641193</v>
+        <v>-1.623677129033441</v>
       </c>
       <c r="JC98" t="n">
-        <v>10.20462165628716</v>
+        <v>6.675253117524337</v>
       </c>
     </row>
     <row r="99">
@@ -79649,10 +79649,10 @@
         <v>0</v>
       </c>
       <c r="JB99" t="n">
-        <v>-0.9291019071641193</v>
+        <v>-1.623677129033441</v>
       </c>
       <c r="JC99" t="n">
-        <v>10.20462167144337</v>
+        <v>6.675253132680538</v>
       </c>
     </row>
     <row r="100">
@@ -80444,10 +80444,10 @@
         <v>0</v>
       </c>
       <c r="JB100" t="n">
-        <v>-0.9291019071641193</v>
+        <v>-1.623677129033441</v>
       </c>
       <c r="JC100" t="n">
-        <v>10.20462143652225</v>
+        <v>6.675252897759426</v>
       </c>
     </row>
     <row r="101">
@@ -81239,10 +81239,10 @@
         <v>0</v>
       </c>
       <c r="JB101" t="n">
-        <v>-0.9291019071641193</v>
+        <v>-1.623677129033441</v>
       </c>
       <c r="JC101" t="n">
-        <v>10.20462149714706</v>
+        <v>6.675252958384229</v>
       </c>
     </row>
     <row r="102">
@@ -82031,13 +82031,13 @@
         </is>
       </c>
       <c r="JA102" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB102" t="n">
-        <v>-0.9291019071641193</v>
+        <v>1.780723568071307</v>
       </c>
       <c r="JC102" t="n">
-        <v>10.20462136831935</v>
+        <v>6.675252829556522</v>
       </c>
     </row>
     <row r="103">
@@ -82826,13 +82826,13 @@
         </is>
       </c>
       <c r="JA103" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB103" t="n">
-        <v>-0.9291019071641193</v>
+        <v>1.780723568071307</v>
       </c>
       <c r="JC103" t="n">
-        <v>10.20462150472516</v>
+        <v>6.67525296596233</v>
       </c>
     </row>
     <row r="104">
@@ -83624,10 +83624,10 @@
         <v>0</v>
       </c>
       <c r="JB104" t="n">
-        <v>-0.9291019071641193</v>
+        <v>-1.023677129033441</v>
       </c>
       <c r="JC104" t="n">
-        <v>10.20462167902147</v>
+        <v>6.675253140258638</v>
       </c>
     </row>
     <row r="105">
@@ -84419,10 +84419,10 @@
         <v>0</v>
       </c>
       <c r="JB105" t="n">
-        <v>-0.9291019071641193</v>
+        <v>-1.023677129033441</v>
       </c>
       <c r="JC105" t="n">
-        <v>10.20462182300538</v>
+        <v>6.675253284242546</v>
       </c>
     </row>
     <row r="106">
@@ -85214,10 +85214,10 @@
         <v>0</v>
       </c>
       <c r="JB106" t="n">
-        <v>-0.9291019071641193</v>
+        <v>-1.623677129033441</v>
       </c>
       <c r="JC106" t="n">
-        <v>10.20462165628716</v>
+        <v>6.675253117524337</v>
       </c>
     </row>
     <row r="107">
@@ -86009,10 +86009,10 @@
         <v>0</v>
       </c>
       <c r="JB107" t="n">
-        <v>-0.9291019071641193</v>
+        <v>-1.623677129033441</v>
       </c>
       <c r="JC107" t="n">
-        <v>10.20462164870907</v>
+        <v>6.675253109946237</v>
       </c>
     </row>
     <row r="108">
@@ -86804,10 +86804,10 @@
         <v>0</v>
       </c>
       <c r="JB108" t="n">
-        <v>-0.9291019071641193</v>
+        <v>-1.623677129033441</v>
       </c>
       <c r="JC108" t="n">
-        <v>10.20462136074125</v>
+        <v>6.675252821978422</v>
       </c>
     </row>
     <row r="109">
@@ -87596,13 +87596,13 @@
         </is>
       </c>
       <c r="JA109" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB109" t="n">
-        <v>-0.9291019071641193</v>
+        <v>1.780723568071307</v>
       </c>
       <c r="JC109" t="n">
-        <v>10.20462137589745</v>
+        <v>6.675252837134623</v>
       </c>
     </row>
     <row r="110">
@@ -88394,10 +88394,10 @@
         <v>0</v>
       </c>
       <c r="JB110" t="n">
-        <v>-0.9291019071641193</v>
+        <v>-1.023677129033441</v>
       </c>
       <c r="JC110" t="n">
-        <v>10.20462160324046</v>
+        <v>6.675253064477634</v>
       </c>
     </row>
     <row r="111">
@@ -89186,13 +89186,13 @@
         </is>
       </c>
       <c r="JA111" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB111" t="n">
-        <v>-0.9291019071641193</v>
+        <v>1.780723568071307</v>
       </c>
       <c r="JC111" t="n">
-        <v>10.20462158808426</v>
+        <v>6.675253049321434</v>
       </c>
     </row>
     <row r="112">
@@ -89984,10 +89984,10 @@
         <v>0</v>
       </c>
       <c r="JB112" t="n">
-        <v>-0.9291019071641193</v>
+        <v>-1.023677129033441</v>
       </c>
       <c r="JC112" t="n">
-        <v>10.20462169417767</v>
+        <v>6.675253155414839</v>
       </c>
     </row>
     <row r="113">
@@ -90776,13 +90776,13 @@
         </is>
       </c>
       <c r="JA113" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB113" t="n">
-        <v>-0.9291019071641193</v>
+        <v>1.780723568071307</v>
       </c>
       <c r="JC113" t="n">
-        <v>10.20462142136605</v>
+        <v>6.675252882603226</v>
       </c>
     </row>
     <row r="114">
@@ -91571,13 +91571,13 @@
         </is>
       </c>
       <c r="JA114" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB114" t="n">
-        <v>-0.9291019071641193</v>
+        <v>1.780723568071307</v>
       </c>
       <c r="JC114" t="n">
-        <v>10.20462151988136</v>
+        <v>6.67525298111853</v>
       </c>
     </row>
     <row r="115">
@@ -92366,13 +92366,13 @@
         </is>
       </c>
       <c r="JA115" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB115" t="n">
-        <v>-0.9291019071641193</v>
+        <v>1.780723568071307</v>
       </c>
       <c r="JC115" t="n">
-        <v>10.20462167144337</v>
+        <v>6.675253132680538</v>
       </c>
     </row>
     <row r="116">
@@ -93161,13 +93161,13 @@
         </is>
       </c>
       <c r="JA116" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB116" t="n">
-        <v>-0.9291019071641193</v>
+        <v>1.780723568071307</v>
       </c>
       <c r="JC116" t="n">
-        <v>10.20462168659957</v>
+        <v>6.675253147836739</v>
       </c>
     </row>
     <row r="117">
@@ -93956,13 +93956,13 @@
         </is>
       </c>
       <c r="JA117" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB117" t="n">
-        <v>-0.9291019071641193</v>
+        <v>1.780723568071307</v>
       </c>
       <c r="JC117" t="n">
-        <v>10.20462166386527</v>
+        <v>6.675253125102438</v>
       </c>
     </row>
     <row r="118">
@@ -94751,13 +94751,13 @@
         </is>
       </c>
       <c r="JA118" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB118" t="n">
-        <v>-0.9291019071641193</v>
+        <v>1.780723568071307</v>
       </c>
       <c r="JC118" t="n">
-        <v>10.20462174722437</v>
+        <v>6.675253208461542</v>
       </c>
     </row>
     <row r="119">
@@ -95549,10 +95549,10 @@
         <v>0</v>
       </c>
       <c r="JB119" t="n">
-        <v>-0.9291019071641193</v>
+        <v>-1.623677129033441</v>
       </c>
       <c r="JC119" t="n">
-        <v>10.20462184573968</v>
+        <v>6.675253306976847</v>
       </c>
     </row>
     <row r="120">
@@ -96344,10 +96344,10 @@
         <v>0</v>
       </c>
       <c r="JB120" t="n">
-        <v>-0.9291019071641193</v>
+        <v>-1.623677129033441</v>
       </c>
       <c r="JC120" t="n">
-        <v>10.20462167902147</v>
+        <v>6.675253140258638</v>
       </c>
     </row>
     <row r="121">
@@ -97136,13 +97136,13 @@
         </is>
       </c>
       <c r="JA121" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB121" t="n">
-        <v>-0.9291019071641193</v>
+        <v>1.180723568071307</v>
       </c>
       <c r="JC121" t="n">
-        <v>10.20462166386527</v>
+        <v>6.675253125102438</v>
       </c>
     </row>
     <row r="122">
@@ -97934,10 +97934,10 @@
         <v>0</v>
       </c>
       <c r="JB122" t="n">
-        <v>-0.9291019071641193</v>
+        <v>-1.623677129033441</v>
       </c>
       <c r="JC122" t="n">
-        <v>10.20462163355286</v>
+        <v>6.675253094790036</v>
       </c>
     </row>
     <row r="123">
@@ -98729,10 +98729,10 @@
         <v>0</v>
       </c>
       <c r="JB123" t="n">
-        <v>-0.9291019071641193</v>
+        <v>-1.623677129033441</v>
       </c>
       <c r="JC123" t="n">
-        <v>10.20462161839666</v>
+        <v>6.675253079633836</v>
       </c>
     </row>
     <row r="124">
@@ -99524,10 +99524,10 @@
         <v>0</v>
       </c>
       <c r="JB124" t="n">
-        <v>-0.9291019071641193</v>
+        <v>-1.623677129033441</v>
       </c>
       <c r="JC124" t="n">
-        <v>10.20462165628716</v>
+        <v>6.675253117524337</v>
       </c>
     </row>
     <row r="125">
@@ -100319,10 +100319,10 @@
         <v>0</v>
       </c>
       <c r="JB125" t="n">
-        <v>-0.9291019071641193</v>
+        <v>-1.623677129033441</v>
       </c>
       <c r="JC125" t="n">
-        <v>10.20462167144337</v>
+        <v>6.675253132680538</v>
       </c>
     </row>
     <row r="126">
@@ -101114,10 +101114,10 @@
         <v>0</v>
       </c>
       <c r="JB126" t="n">
-        <v>-0.9291019071641193</v>
+        <v>-1.623677129033441</v>
       </c>
       <c r="JC126" t="n">
-        <v>10.20462166386527</v>
+        <v>6.675253125102438</v>
       </c>
     </row>
   </sheetData>

--- a/out/MLP-S4_repeat_2_000007.xlsx
+++ b/out/MLP-S4_repeat_2_000007.xlsx
@@ -2534,7 +2534,7 @@
         <v>0</v>
       </c>
       <c r="JB2" t="n">
-        <v>-0.9291019071641193</v>
+        <v>-0.471384164912539</v>
       </c>
       <c r="JC2" t="n">
         <v>0</v>
@@ -3329,7 +3329,7 @@
         <v>0</v>
       </c>
       <c r="JB3" t="n">
-        <v>-0.9291019071641193</v>
+        <v>-0.471384164912539</v>
       </c>
       <c r="JC3" t="n">
         <v>0</v>
@@ -4117,14 +4117,14 @@
       </c>
       <c r="IZ4" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA4" t="n">
         <v>0</v>
       </c>
       <c r="JB4" t="n">
-        <v>-0.9291019071641193</v>
+        <v>0.3845367972155144</v>
       </c>
       <c r="JC4" t="n">
         <v>0</v>
@@ -4919,7 +4919,7 @@
         <v>1</v>
       </c>
       <c r="JB5" t="n">
-        <v>3.415552302146114</v>
+        <v>0.5845367972155144</v>
       </c>
       <c r="JC5" t="n">
         <v>0</v>
@@ -5714,7 +5714,7 @@
         <v>0</v>
       </c>
       <c r="JB6" t="n">
-        <v>-0.3291019071641194</v>
+        <v>0.5845367972155144</v>
       </c>
       <c r="JC6" t="n">
         <v>0</v>
@@ -6509,7 +6509,7 @@
         <v>0</v>
       </c>
       <c r="JB7" t="n">
-        <v>-0.3291019071641194</v>
+        <v>-0.271384164912539</v>
       </c>
       <c r="JC7" t="n">
         <v>0</v>
@@ -7304,7 +7304,7 @@
         <v>0</v>
       </c>
       <c r="JB8" t="n">
-        <v>-0.9291019071641193</v>
+        <v>-0.471384164912539</v>
       </c>
       <c r="JC8" t="n">
         <v>0</v>
@@ -8099,7 +8099,7 @@
         <v>0</v>
       </c>
       <c r="JB9" t="n">
-        <v>-0.9291019071641193</v>
+        <v>-0.471384164912539</v>
       </c>
       <c r="JC9" t="n">
         <v>0</v>
@@ -8894,7 +8894,7 @@
         <v>0</v>
       </c>
       <c r="JB10" t="n">
-        <v>-0.9291019071641193</v>
+        <v>-0.471384164912539</v>
       </c>
       <c r="JC10" t="n">
         <v>0</v>
@@ -9689,7 +9689,7 @@
         <v>0</v>
       </c>
       <c r="JB11" t="n">
-        <v>-0.9291019071641193</v>
+        <v>-0.471384164912539</v>
       </c>
       <c r="JC11" t="n">
         <v>0</v>
@@ -10484,7 +10484,7 @@
         <v>0</v>
       </c>
       <c r="JB12" t="n">
-        <v>-0.9291019071641193</v>
+        <v>-0.471384164912539</v>
       </c>
       <c r="JC12" t="n">
         <v>0</v>
@@ -11279,7 +11279,7 @@
         <v>0</v>
       </c>
       <c r="JB13" t="n">
-        <v>-0.9291019071641193</v>
+        <v>-0.471384164912539</v>
       </c>
       <c r="JC13" t="n">
         <v>0</v>
@@ -12074,7 +12074,7 @@
         <v>0</v>
       </c>
       <c r="JB14" t="n">
-        <v>-0.9291019071641193</v>
+        <v>-0.471384164912539</v>
       </c>
       <c r="JC14" t="n">
         <v>0</v>
@@ -12869,7 +12869,7 @@
         <v>0</v>
       </c>
       <c r="JB15" t="n">
-        <v>-0.9291019071641193</v>
+        <v>-0.471384164912539</v>
       </c>
       <c r="JC15" t="n">
         <v>0</v>
@@ -13664,7 +13664,7 @@
         <v>0</v>
       </c>
       <c r="JB16" t="n">
-        <v>-0.9291019071641193</v>
+        <v>-0.471384164912539</v>
       </c>
       <c r="JC16" t="n">
         <v>0</v>
@@ -14459,7 +14459,7 @@
         <v>0</v>
       </c>
       <c r="JB17" t="n">
-        <v>-0.9291019071641193</v>
+        <v>-0.471384164912539</v>
       </c>
       <c r="JC17" t="n">
         <v>0</v>
@@ -15254,7 +15254,7 @@
         <v>0</v>
       </c>
       <c r="JB18" t="n">
-        <v>-0.9291019071641193</v>
+        <v>-0.471384164912539</v>
       </c>
       <c r="JC18" t="n">
         <v>0</v>
@@ -16049,7 +16049,7 @@
         <v>0</v>
       </c>
       <c r="JB19" t="n">
-        <v>-0.9291019071641193</v>
+        <v>-0.471384164912539</v>
       </c>
       <c r="JC19" t="n">
         <v>0</v>
@@ -16844,7 +16844,7 @@
         <v>0</v>
       </c>
       <c r="JB20" t="n">
-        <v>-0.9291019071641193</v>
+        <v>-0.471384164912539</v>
       </c>
       <c r="JC20" t="n">
         <v>0</v>
@@ -17639,7 +17639,7 @@
         <v>0</v>
       </c>
       <c r="JB21" t="n">
-        <v>-0.9291019071641193</v>
+        <v>-0.471384164912539</v>
       </c>
       <c r="JC21" t="n">
         <v>0</v>
@@ -18434,7 +18434,7 @@
         <v>0</v>
       </c>
       <c r="JB22" t="n">
-        <v>-0.9291019071641193</v>
+        <v>0.5845367972155144</v>
       </c>
       <c r="JC22" t="n">
         <v>0</v>
@@ -19229,7 +19229,7 @@
         <v>1</v>
       </c>
       <c r="JB23" t="n">
-        <v>3.415552302146114</v>
+        <v>0.5845367972155144</v>
       </c>
       <c r="JC23" t="n">
         <v>0</v>
@@ -20024,7 +20024,7 @@
         <v>0</v>
       </c>
       <c r="JB24" t="n">
-        <v>-0.3291019071641194</v>
+        <v>0.5845367972155144</v>
       </c>
       <c r="JC24" t="n">
         <v>0</v>
@@ -20819,7 +20819,7 @@
         <v>0</v>
       </c>
       <c r="JB25" t="n">
-        <v>-0.3291019071641194</v>
+        <v>-0.271384164912539</v>
       </c>
       <c r="JC25" t="n">
         <v>0</v>
@@ -21614,7 +21614,7 @@
         <v>0</v>
       </c>
       <c r="JB26" t="n">
-        <v>-0.9291019071641193</v>
+        <v>-0.271384164912539</v>
       </c>
       <c r="JC26" t="n">
         <v>0</v>
@@ -22409,7 +22409,7 @@
         <v>0</v>
       </c>
       <c r="JB27" t="n">
-        <v>-0.9291019071641193</v>
+        <v>-0.471384164912539</v>
       </c>
       <c r="JC27" t="n">
         <v>0</v>
@@ -23204,7 +23204,7 @@
         <v>0</v>
       </c>
       <c r="JB28" t="n">
-        <v>-0.9291019071641193</v>
+        <v>-0.471384164912539</v>
       </c>
       <c r="JC28" t="n">
         <v>0</v>
@@ -23999,7 +23999,7 @@
         <v>0</v>
       </c>
       <c r="JB29" t="n">
-        <v>-0.9291019071641193</v>
+        <v>-0.471384164912539</v>
       </c>
       <c r="JC29" t="n">
         <v>0</v>
@@ -24794,7 +24794,7 @@
         <v>0</v>
       </c>
       <c r="JB30" t="n">
-        <v>-0.9291019071641193</v>
+        <v>-0.471384164912539</v>
       </c>
       <c r="JC30" t="n">
         <v>0</v>
@@ -25589,7 +25589,7 @@
         <v>0</v>
       </c>
       <c r="JB31" t="n">
-        <v>-0.9291019071641193</v>
+        <v>-0.471384164912539</v>
       </c>
       <c r="JC31" t="n">
         <v>0</v>
@@ -26384,7 +26384,7 @@
         <v>0</v>
       </c>
       <c r="JB32" t="n">
-        <v>-0.9291019071641193</v>
+        <v>-0.471384164912539</v>
       </c>
       <c r="JC32" t="n">
         <v>0</v>
@@ -27179,7 +27179,7 @@
         <v>0</v>
       </c>
       <c r="JB33" t="n">
-        <v>-0.9291019071641193</v>
+        <v>-0.471384164912539</v>
       </c>
       <c r="JC33" t="n">
         <v>0</v>
@@ -27974,7 +27974,7 @@
         <v>0</v>
       </c>
       <c r="JB34" t="n">
-        <v>-0.9291019071641193</v>
+        <v>-0.471384164912539</v>
       </c>
       <c r="JC34" t="n">
         <v>0</v>
@@ -28769,7 +28769,7 @@
         <v>0</v>
       </c>
       <c r="JB35" t="n">
-        <v>-0.9291019071641193</v>
+        <v>0.5845367972155144</v>
       </c>
       <c r="JC35" t="n">
         <v>0</v>
@@ -29564,7 +29564,7 @@
         <v>1</v>
       </c>
       <c r="JB36" t="n">
-        <v>3.415552302146114</v>
+        <v>1.440457759343568</v>
       </c>
       <c r="JC36" t="n">
         <v>0</v>
@@ -30359,7 +30359,7 @@
         <v>1</v>
       </c>
       <c r="JB37" t="n">
-        <v>3.415552302146114</v>
+        <v>2.296378721471621</v>
       </c>
       <c r="JC37" t="n">
         <v>0</v>
@@ -31154,7 +31154,7 @@
         <v>1</v>
       </c>
       <c r="JB38" t="n">
-        <v>3.415552302146114</v>
+        <v>2.296378721471621</v>
       </c>
       <c r="JC38" t="n">
         <v>0</v>
@@ -31949,10 +31949,10 @@
         <v>1</v>
       </c>
       <c r="JB39" t="n">
-        <v>3.415552302146114</v>
+        <v>2.296378721471621</v>
       </c>
       <c r="JC39" t="n">
-        <v>-0.0003604635853798827</v>
+        <v>-0.0002751175154725788</v>
       </c>
     </row>
     <row r="40">
@@ -32733,7 +32733,7 @@
         <v>0</v>
       </c>
       <c r="IY40" t="n">
-        <v>4.155612693188337</v>
+        <v>3.171698555222005</v>
       </c>
       <c r="IZ40" t="inlineStr">
         <is>
@@ -32744,10 +32744,10 @@
         <v>1</v>
       </c>
       <c r="JB40" t="n">
-        <v>3.415552302146114</v>
+        <v>2.296378721471621</v>
       </c>
       <c r="JC40" t="n">
-        <v>8.317649365197576</v>
+        <v>6.348300135573369</v>
       </c>
     </row>
     <row r="41">
@@ -33528,7 +33528,7 @@
         <v>0</v>
       </c>
       <c r="IY41" t="n">
-        <v>0.6231526832897226</v>
+        <v>0.4756103692814754</v>
       </c>
       <c r="IZ41" t="inlineStr">
         <is>
@@ -33539,10 +33539,10 @@
         <v>1</v>
       </c>
       <c r="JB41" t="n">
-        <v>3.415552302146114</v>
+        <v>2.296378721471621</v>
       </c>
       <c r="JC41" t="n">
-        <v>5.402764483231868</v>
+        <v>4.12356531166803</v>
       </c>
     </row>
     <row r="42">
@@ -34323,7 +34323,7 @@
         <v>0</v>
       </c>
       <c r="IY42" t="n">
-        <v>0.7791436148826281</v>
+        <v>0.5946677152079944</v>
       </c>
       <c r="IZ42" t="inlineStr">
         <is>
@@ -34334,10 +34334,10 @@
         <v>1</v>
       </c>
       <c r="JB42" t="n">
-        <v>3.415552302146114</v>
+        <v>2.296378721471621</v>
       </c>
       <c r="JC42" t="n">
-        <v>6.337997990699301</v>
+        <v>4.837365903046035</v>
       </c>
     </row>
     <row r="43">
@@ -35118,7 +35118,7 @@
         <v>0</v>
       </c>
       <c r="IY43" t="n">
-        <v>1.116898676922276</v>
+        <v>0.8524533495975014</v>
       </c>
       <c r="IZ43" t="inlineStr">
         <is>
@@ -35129,10 +35129,10 @@
         <v>1</v>
       </c>
       <c r="JB43" t="n">
-        <v>3.415552302146114</v>
+        <v>2.296378721471621</v>
       </c>
       <c r="JC43" t="n">
-        <v>7.793091434888637</v>
+        <v>5.947940484345215</v>
       </c>
     </row>
     <row r="44">
@@ -35913,7 +35913,7 @@
         <v>0</v>
       </c>
       <c r="IY44" t="n">
-        <v>1.194860349256982</v>
+        <v>0.9119558822331834</v>
       </c>
       <c r="IZ44" t="inlineStr">
         <is>
@@ -35924,10 +35924,10 @@
         <v>1</v>
       </c>
       <c r="JB44" t="n">
-        <v>3.415552302146114</v>
+        <v>2.296378721471621</v>
       </c>
       <c r="JC44" t="n">
-        <v>9.06599673043802</v>
+        <v>6.91946315325602</v>
       </c>
     </row>
     <row r="45">
@@ -36708,7 +36708,7 @@
         <v>0</v>
       </c>
       <c r="IY45" t="n">
-        <v>1.266311134954735</v>
+        <v>0.9664894219458098</v>
       </c>
       <c r="IZ45" t="inlineStr">
         <is>
@@ -36719,10 +36719,10 @@
         <v>1</v>
       </c>
       <c r="JB45" t="n">
-        <v>2.815552302146114</v>
+        <v>2.296378721471621</v>
       </c>
       <c r="JC45" t="n">
-        <v>10.40384906616079</v>
+        <v>7.94055590315098</v>
       </c>
     </row>
     <row r="46">
@@ -37503,7 +37503,7 @@
         <v>0</v>
       </c>
       <c r="IY46" t="n">
-        <v>0.5714619975069256</v>
+        <v>0.4361587006051614</v>
       </c>
       <c r="IZ46" t="inlineStr">
         <is>
@@ -37514,10 +37514,10 @@
         <v>1</v>
       </c>
       <c r="JB46" t="n">
-        <v>2.815552302146114</v>
+        <v>2.096378721471621</v>
       </c>
       <c r="JC46" t="n">
-        <v>10.27941095943332</v>
+        <v>7.845580589561809</v>
       </c>
     </row>
     <row r="47">
@@ -38298,7 +38298,7 @@
         <v>0</v>
       </c>
       <c r="IY47" t="n">
-        <v>0.2759900252444427</v>
+        <v>0.2106447170866213</v>
       </c>
       <c r="IZ47" t="inlineStr">
         <is>
@@ -38309,10 +38309,10 @@
         <v>1</v>
       </c>
       <c r="JB47" t="n">
-        <v>2.815552302146114</v>
+        <v>2.096378721471621</v>
       </c>
       <c r="JC47" t="n">
-        <v>10.25948086265405</v>
+        <v>7.83036926964175</v>
       </c>
     </row>
     <row r="48">
@@ -39093,7 +39093,7 @@
         <v>0</v>
       </c>
       <c r="IY48" t="n">
-        <v>0.1315016431784234</v>
+        <v>0.1003665492948865</v>
       </c>
       <c r="IZ48" t="inlineStr">
         <is>
@@ -39104,10 +39104,10 @@
         <v>1</v>
       </c>
       <c r="JB48" t="n">
-        <v>2.815552302146114</v>
+        <v>1.240457759343568</v>
       </c>
       <c r="JC48" t="n">
-        <v>10.24627366207712</v>
+        <v>7.820289082689608</v>
       </c>
     </row>
     <row r="49">
@@ -39888,7 +39888,7 @@
         <v>0</v>
       </c>
       <c r="IY49" t="n">
-        <v>0.03896265639495582</v>
+        <v>0.02973754525910433</v>
       </c>
       <c r="IZ49" t="inlineStr">
         <is>
@@ -39899,10 +39899,10 @@
         <v>0</v>
       </c>
       <c r="JB49" t="n">
-        <v>-0.9291019071641193</v>
+        <v>0.3845367972155144</v>
       </c>
       <c r="JC49" t="n">
-        <v>10.19255798453488</v>
+        <v>7.77929144151685</v>
       </c>
     </row>
     <row r="50">
@@ -40683,7 +40683,7 @@
         <v>0</v>
       </c>
       <c r="IY50" t="n">
-        <v>0.02577282474534589</v>
+        <v>0.01967075773815177</v>
       </c>
       <c r="IZ50" t="inlineStr">
         <is>
@@ -40694,10 +40694,10 @@
         <v>0</v>
       </c>
       <c r="JB50" t="n">
-        <v>-0.9291019071641193</v>
+        <v>-0.471384164912539</v>
       </c>
       <c r="JC50" t="n">
-        <v>10.20511990686067</v>
+        <v>7.788879157773713</v>
       </c>
     </row>
     <row r="51">
@@ -41478,7 +41478,7 @@
         <v>0</v>
       </c>
       <c r="IY51" t="n">
-        <v>0.01318983812480389</v>
+        <v>0.01006578062694764</v>
       </c>
       <c r="IZ51" t="inlineStr">
         <is>
@@ -41489,10 +41489,10 @@
         <v>0</v>
       </c>
       <c r="JB51" t="n">
-        <v>-0.9291019071641193</v>
+        <v>-0.471384164912539</v>
       </c>
       <c r="JC51" t="n">
-        <v>10.20570857652375</v>
+        <v>7.789327268064661</v>
       </c>
     </row>
     <row r="52">
@@ -42273,7 +42273,7 @@
         <v>0</v>
       </c>
       <c r="IY52" t="n">
-        <v>0.006744669631670948</v>
+        <v>0.005146090157384079</v>
       </c>
       <c r="IZ52" t="inlineStr">
         <is>
@@ -42284,10 +42284,10 @@
         <v>0</v>
       </c>
       <c r="JB52" t="n">
-        <v>-0.9291019071641193</v>
+        <v>-0.471384164912539</v>
       </c>
       <c r="JC52" t="n">
-        <v>10.2060002284351</v>
+        <v>7.789548684211398</v>
       </c>
     </row>
     <row r="53">
@@ -43068,7 +43068,7 @@
         <v>0</v>
       </c>
       <c r="IY53" t="n">
-        <v>0.00253207824239737</v>
+        <v>0.001931868503071262</v>
       </c>
       <c r="IZ53" t="inlineStr">
         <is>
@@ -43079,10 +43079,10 @@
         <v>0</v>
       </c>
       <c r="JB53" t="n">
-        <v>-0.9291019071641193</v>
+        <v>-0.471384164912539</v>
       </c>
       <c r="JC53" t="n">
-        <v>10.2043153590409</v>
+        <v>7.788261421135045</v>
       </c>
     </row>
     <row r="54">
@@ -43863,7 +43863,7 @@
         <v>0</v>
       </c>
       <c r="IY54" t="n">
-        <v>0.001377710017885418</v>
+        <v>0.001050182644913753</v>
       </c>
       <c r="IZ54" t="inlineStr">
         <is>
@@ -43874,10 +43874,10 @@
         <v>0</v>
       </c>
       <c r="JB54" t="n">
-        <v>-0.9291019071641193</v>
+        <v>-0.471384164912539</v>
       </c>
       <c r="JC54" t="n">
-        <v>10.20453735570176</v>
+        <v>7.788429664455926</v>
       </c>
     </row>
     <row r="55">
@@ -44658,7 +44658,7 @@
         <v>0</v>
       </c>
       <c r="IY55" t="n">
-        <v>0.0006609836985678793</v>
+        <v>0.0005036271683573302</v>
       </c>
       <c r="IZ55" t="inlineStr">
         <is>
@@ -44669,10 +44669,10 @@
         <v>0</v>
       </c>
       <c r="JB55" t="n">
-        <v>-0.9291019071641193</v>
+        <v>-0.471384164912539</v>
       </c>
       <c r="JC55" t="n">
-        <v>10.20448070844907</v>
+        <v>7.788385243403678</v>
       </c>
     </row>
     <row r="56">
@@ -45453,7 +45453,7 @@
         <v>0</v>
       </c>
       <c r="IY56" t="n">
-        <v>0.0004072771942052819</v>
+        <v>0.0003098656375792129</v>
       </c>
       <c r="IZ56" t="inlineStr">
         <is>
@@ -45464,10 +45464,10 @@
         <v>0</v>
       </c>
       <c r="JB56" t="n">
-        <v>-0.9291019071641193</v>
+        <v>-0.471384164912539</v>
       </c>
       <c r="JC56" t="n">
-        <v>10.20463415717052</v>
+        <v>7.788501109671133</v>
       </c>
     </row>
     <row r="57">
@@ -46248,7 +46248,7 @@
         <v>0</v>
       </c>
       <c r="IY57" t="n">
-        <v>0.0002111675230719449</v>
+        <v>0.0001596990651976723</v>
       </c>
       <c r="IZ57" t="inlineStr">
         <is>
@@ -46259,10 +46259,10 @@
         <v>0</v>
       </c>
       <c r="JB57" t="n">
-        <v>-0.9291019071641193</v>
+        <v>0.3845367972155144</v>
       </c>
       <c r="JC57" t="n">
-        <v>10.2046479909593</v>
+        <v>7.788510459224481</v>
       </c>
     </row>
     <row r="58">
@@ -47043,7 +47043,7 @@
         <v>0</v>
       </c>
       <c r="IY58" t="n">
-        <v>9.990477873244368e-05</v>
+        <v>7.492745046281422e-05</v>
       </c>
       <c r="IZ58" t="inlineStr">
         <is>
@@ -47054,10 +47054,10 @@
         <v>1</v>
       </c>
       <c r="JB58" t="n">
-        <v>3.415552302146114</v>
+        <v>1.440457759343568</v>
       </c>
       <c r="JC58" t="n">
-        <v>10.20463649766222</v>
+        <v>7.788500511950513</v>
       </c>
     </row>
     <row r="59">
@@ -47838,7 +47838,7 @@
         <v>0</v>
       </c>
       <c r="IY59" t="n">
-        <v>6.151561164366101e-05</v>
+        <v>4.616585511050847e-05</v>
       </c>
       <c r="IZ59" t="inlineStr">
         <is>
@@ -47849,10 +47849,10 @@
         <v>1</v>
       </c>
       <c r="JB59" t="n">
-        <v>3.415552302146114</v>
+        <v>1.440457759343568</v>
       </c>
       <c r="JC59" t="n">
-        <v>10.20466085784762</v>
+        <v>7.788517881024123</v>
       </c>
     </row>
     <row r="60">
@@ -48633,7 +48633,7 @@
         <v>0</v>
       </c>
       <c r="IY60" t="n">
-        <v>2.530589321855379e-05</v>
+        <v>1.831222555273368e-05</v>
       </c>
       <c r="IZ60" t="inlineStr">
         <is>
@@ -48644,10 +48644,10 @@
         <v>0</v>
       </c>
       <c r="JB60" t="n">
-        <v>-0.3291019071641194</v>
+        <v>0.5845367972155144</v>
       </c>
       <c r="JC60" t="n">
-        <v>10.20464979643704</v>
+        <v>7.78850830584022</v>
       </c>
     </row>
     <row r="61">
@@ -49428,7 +49428,7 @@
         <v>0</v>
       </c>
       <c r="IY61" t="n">
-        <v>8.38179904731087e-06</v>
+        <v>5.293691574854516e-06</v>
       </c>
       <c r="IZ61" t="inlineStr">
         <is>
@@ -49439,10 +49439,10 @@
         <v>0</v>
       </c>
       <c r="JB61" t="n">
-        <v>-0.3291019071641194</v>
+        <v>-0.271384164912539</v>
       </c>
       <c r="JC61" t="n">
-        <v>10.2046410971978</v>
+        <v>7.788500565199114</v>
       </c>
     </row>
     <row r="62">
@@ -50223,7 +50223,7 @@
         <v>0</v>
       </c>
       <c r="IY62" t="n">
-        <v>2.788397616378431e-06</v>
+        <v>5.63141154556023e-07</v>
       </c>
       <c r="IZ62" t="inlineStr">
         <is>
@@ -50234,10 +50234,10 @@
         <v>0</v>
       </c>
       <c r="JB62" t="n">
-        <v>-0.9291019071641193</v>
+        <v>-0.471384164912539</v>
       </c>
       <c r="JC62" t="n">
-        <v>10.20463725475757</v>
+        <v>7.788496392027522</v>
       </c>
     </row>
     <row r="63">
@@ -51018,7 +51018,7 @@
         <v>0</v>
       </c>
       <c r="IY63" t="n">
-        <v>-2.093548687745288e-06</v>
+        <v>-3.062365791830193e-06</v>
       </c>
       <c r="IZ63" t="inlineStr">
         <is>
@@ -51029,10 +51029,10 @@
         <v>0</v>
       </c>
       <c r="JB63" t="n">
-        <v>-0.9291019071641193</v>
+        <v>-0.471384164912539</v>
       </c>
       <c r="JC63" t="n">
-        <v>10.20463124333098</v>
+        <v>7.788490669748491</v>
       </c>
     </row>
     <row r="64">
@@ -51813,7 +51813,7 @@
         <v>0</v>
       </c>
       <c r="IY64" t="n">
-        <v>-3.107779831880603e-06</v>
+        <v>-4.053889915940302e-06</v>
       </c>
       <c r="IZ64" t="inlineStr">
         <is>
@@ -51824,10 +51824,10 @@
         <v>0</v>
       </c>
       <c r="JB64" t="n">
-        <v>-0.9291019071641193</v>
+        <v>0.3845367972155144</v>
       </c>
       <c r="JC64" t="n">
-        <v>10.20462615008884</v>
+        <v>7.788485600393122</v>
       </c>
     </row>
     <row r="65">
@@ -52619,10 +52619,10 @@
         <v>1</v>
       </c>
       <c r="JB65" t="n">
-        <v>3.415552302146114</v>
+        <v>1.440457759343568</v>
       </c>
       <c r="JC65" t="n">
-        <v>10.20462178511487</v>
+        <v>7.788481235419154</v>
       </c>
     </row>
     <row r="66">
@@ -53414,10 +53414,10 @@
         <v>1</v>
       </c>
       <c r="JB66" t="n">
-        <v>3.415552302146114</v>
+        <v>2.296378721471621</v>
       </c>
       <c r="JC66" t="n">
-        <v>10.20462287636133</v>
+        <v>7.78848232666561</v>
       </c>
     </row>
     <row r="67">
@@ -54209,10 +54209,10 @@
         <v>1</v>
       </c>
       <c r="JB67" t="n">
-        <v>3.415552302146114</v>
+        <v>1.440457759343568</v>
       </c>
       <c r="JC67" t="n">
-        <v>10.20462218675419</v>
+        <v>7.788481637058474</v>
       </c>
     </row>
     <row r="68">
@@ -55004,10 +55004,10 @@
         <v>0</v>
       </c>
       <c r="JB68" t="n">
-        <v>-0.3291019071641194</v>
+        <v>0.5845367972155144</v>
       </c>
       <c r="JC68" t="n">
-        <v>10.20462221706659</v>
+        <v>7.788481667370876</v>
       </c>
     </row>
     <row r="69">
@@ -55799,10 +55799,10 @@
         <v>0</v>
       </c>
       <c r="JB69" t="n">
-        <v>-0.3291019071641194</v>
+        <v>-0.471384164912539</v>
       </c>
       <c r="JC69" t="n">
-        <v>10.20462202761409</v>
+        <v>7.788481477918366</v>
       </c>
     </row>
     <row r="70">
@@ -56594,10 +56594,10 @@
         <v>0</v>
       </c>
       <c r="JB70" t="n">
-        <v>-0.9291019071641193</v>
+        <v>-0.471384164912539</v>
       </c>
       <c r="JC70" t="n">
-        <v>10.20462208066079</v>
+        <v>7.788481530965069</v>
       </c>
     </row>
     <row r="71">
@@ -57389,10 +57389,10 @@
         <v>0</v>
       </c>
       <c r="JB71" t="n">
-        <v>-0.9291019071641193</v>
+        <v>-0.471384164912539</v>
       </c>
       <c r="JC71" t="n">
-        <v>10.20462213370749</v>
+        <v>7.78848158401177</v>
       </c>
     </row>
     <row r="72">
@@ -58184,10 +58184,10 @@
         <v>0</v>
       </c>
       <c r="JB72" t="n">
-        <v>-0.9291019071641193</v>
+        <v>-0.471384164912539</v>
       </c>
       <c r="JC72" t="n">
-        <v>10.20462209581699</v>
+        <v>7.788481546121269</v>
       </c>
     </row>
     <row r="73">
@@ -58979,10 +58979,10 @@
         <v>0</v>
       </c>
       <c r="JB73" t="n">
-        <v>-0.9291019071641193</v>
+        <v>-0.471384164912539</v>
       </c>
       <c r="JC73" t="n">
-        <v>10.20462196698928</v>
+        <v>7.788481417293563</v>
       </c>
     </row>
     <row r="74">
@@ -59774,10 +59774,10 @@
         <v>0</v>
       </c>
       <c r="JB74" t="n">
-        <v>-0.9291019071641193</v>
+        <v>-0.471384164912539</v>
       </c>
       <c r="JC74" t="n">
-        <v>10.20462182300538</v>
+        <v>7.788481273309656</v>
       </c>
     </row>
     <row r="75">
@@ -60569,10 +60569,10 @@
         <v>0</v>
       </c>
       <c r="JB75" t="n">
-        <v>-0.9291019071641193</v>
+        <v>-0.471384164912539</v>
       </c>
       <c r="JC75" t="n">
-        <v>10.20462166386527</v>
+        <v>7.788481114169548</v>
       </c>
     </row>
     <row r="76">
@@ -61364,10 +61364,10 @@
         <v>0</v>
       </c>
       <c r="JB76" t="n">
-        <v>-0.9291019071641193</v>
+        <v>-0.471384164912539</v>
       </c>
       <c r="JC76" t="n">
-        <v>10.20462171691197</v>
+        <v>7.788481167216251</v>
       </c>
     </row>
     <row r="77">
@@ -62159,10 +62159,10 @@
         <v>0</v>
       </c>
       <c r="JB77" t="n">
-        <v>-0.9291019071641193</v>
+        <v>-0.471384164912539</v>
       </c>
       <c r="JC77" t="n">
-        <v>10.20462166386527</v>
+        <v>7.788481114169548</v>
       </c>
     </row>
     <row r="78">
@@ -62954,10 +62954,10 @@
         <v>0</v>
       </c>
       <c r="JB78" t="n">
-        <v>-0.9291019071641193</v>
+        <v>-0.471384164912539</v>
       </c>
       <c r="JC78" t="n">
-        <v>10.20462166386527</v>
+        <v>7.788481114169548</v>
       </c>
     </row>
     <row r="79">
@@ -63749,10 +63749,10 @@
         <v>0</v>
       </c>
       <c r="JB79" t="n">
-        <v>-0.9291019071641193</v>
+        <v>-0.471384164912539</v>
       </c>
       <c r="JC79" t="n">
-        <v>10.20462148199086</v>
+        <v>7.788480932295138</v>
       </c>
     </row>
     <row r="80">
@@ -64544,10 +64544,10 @@
         <v>0</v>
       </c>
       <c r="JB80" t="n">
-        <v>-0.9291019071641193</v>
+        <v>-0.471384164912539</v>
       </c>
       <c r="JC80" t="n">
-        <v>10.20462164870907</v>
+        <v>7.788481099013347</v>
       </c>
     </row>
     <row r="81">
@@ -65339,10 +65339,10 @@
         <v>0</v>
       </c>
       <c r="JB81" t="n">
-        <v>-0.9291019071641193</v>
+        <v>-0.471384164912539</v>
       </c>
       <c r="JC81" t="n">
-        <v>10.20462184573968</v>
+        <v>7.788481296043956</v>
       </c>
     </row>
     <row r="82">
@@ -66134,10 +66134,10 @@
         <v>0</v>
       </c>
       <c r="JB82" t="n">
-        <v>-0.9291019071641193</v>
+        <v>-0.471384164912539</v>
       </c>
       <c r="JC82" t="n">
-        <v>10.20462168659957</v>
+        <v>7.788481136903848</v>
       </c>
     </row>
     <row r="83">
@@ -66929,10 +66929,10 @@
         <v>0</v>
       </c>
       <c r="JB83" t="n">
-        <v>-0.9291019071641193</v>
+        <v>-0.471384164912539</v>
       </c>
       <c r="JC83" t="n">
-        <v>10.20462172449007</v>
+        <v>7.78848117479435</v>
       </c>
     </row>
     <row r="84">
@@ -67724,10 +67724,10 @@
         <v>0</v>
       </c>
       <c r="JB84" t="n">
-        <v>-0.9291019071641193</v>
+        <v>-0.471384164912539</v>
       </c>
       <c r="JC84" t="n">
-        <v>10.20462192152068</v>
+        <v>7.788481371824961</v>
       </c>
     </row>
     <row r="85">
@@ -68519,10 +68519,10 @@
         <v>0</v>
       </c>
       <c r="JB85" t="n">
-        <v>-0.9291019071641193</v>
+        <v>-0.471384164912539</v>
       </c>
       <c r="JC85" t="n">
-        <v>10.20462189878638</v>
+        <v>7.78848134909066</v>
       </c>
     </row>
     <row r="86">
@@ -69314,10 +69314,10 @@
         <v>0</v>
       </c>
       <c r="JB86" t="n">
-        <v>-0.9291019071641193</v>
+        <v>-0.471384164912539</v>
       </c>
       <c r="JC86" t="n">
-        <v>10.20462174722437</v>
+        <v>7.788481197528651</v>
       </c>
     </row>
     <row r="87">
@@ -70109,10 +70109,10 @@
         <v>0</v>
       </c>
       <c r="JB87" t="n">
-        <v>-0.9291019071641193</v>
+        <v>-0.471384164912539</v>
       </c>
       <c r="JC87" t="n">
-        <v>10.20462167144337</v>
+        <v>7.788481121747648</v>
       </c>
     </row>
     <row r="88">
@@ -70904,10 +70904,10 @@
         <v>0</v>
       </c>
       <c r="JB88" t="n">
-        <v>-0.9291019071641193</v>
+        <v>-0.471384164912539</v>
       </c>
       <c r="JC88" t="n">
-        <v>10.20462176995867</v>
+        <v>7.788481220262952</v>
       </c>
     </row>
     <row r="89">
@@ -71699,10 +71699,10 @@
         <v>0</v>
       </c>
       <c r="JB89" t="n">
-        <v>-0.9291019071641193</v>
+        <v>-0.471384164912539</v>
       </c>
       <c r="JC89" t="n">
-        <v>10.20462177753677</v>
+        <v>7.788481227841054</v>
       </c>
     </row>
     <row r="90">
@@ -72494,10 +72494,10 @@
         <v>0</v>
       </c>
       <c r="JB90" t="n">
-        <v>-0.9291019071641193</v>
+        <v>-0.471384164912539</v>
       </c>
       <c r="JC90" t="n">
-        <v>10.20462204277029</v>
+        <v>7.788481493074566</v>
       </c>
     </row>
     <row r="91">
@@ -73289,10 +73289,10 @@
         <v>0</v>
       </c>
       <c r="JB91" t="n">
-        <v>-0.9291019071641193</v>
+        <v>-0.471384164912539</v>
       </c>
       <c r="JC91" t="n">
-        <v>10.20462174722437</v>
+        <v>7.788481197528651</v>
       </c>
     </row>
     <row r="92">
@@ -74084,10 +74084,10 @@
         <v>0</v>
       </c>
       <c r="JB92" t="n">
-        <v>-0.9291019071641193</v>
+        <v>-0.471384164912539</v>
       </c>
       <c r="JC92" t="n">
-        <v>10.20462198972358</v>
+        <v>7.788481440027865</v>
       </c>
     </row>
     <row r="93">
@@ -74879,10 +74879,10 @@
         <v>0</v>
       </c>
       <c r="JB93" t="n">
-        <v>-0.9291019071641193</v>
+        <v>0.5845367972155144</v>
       </c>
       <c r="JC93" t="n">
-        <v>10.20462207308269</v>
+        <v>7.788481523386968</v>
       </c>
     </row>
     <row r="94">
@@ -75674,10 +75674,10 @@
         <v>1</v>
       </c>
       <c r="JB94" t="n">
-        <v>3.415552302146114</v>
+        <v>0.5845367972155144</v>
       </c>
       <c r="JC94" t="n">
-        <v>10.20462190636448</v>
+        <v>7.788481356668759</v>
       </c>
     </row>
     <row r="95">
@@ -76469,10 +76469,10 @@
         <v>0</v>
       </c>
       <c r="JB95" t="n">
-        <v>-0.3291019071641194</v>
+        <v>0.5845367972155144</v>
       </c>
       <c r="JC95" t="n">
-        <v>10.20462209581699</v>
+        <v>7.788481546121269</v>
       </c>
     </row>
     <row r="96">
@@ -77264,10 +77264,10 @@
         <v>0</v>
       </c>
       <c r="JB96" t="n">
-        <v>-0.3291019071641194</v>
+        <v>-0.271384164912539</v>
       </c>
       <c r="JC96" t="n">
-        <v>10.20462174722437</v>
+        <v>7.788481197528651</v>
       </c>
     </row>
     <row r="97">
@@ -78059,10 +78059,10 @@
         <v>0</v>
       </c>
       <c r="JB97" t="n">
-        <v>-0.9291019071641193</v>
+        <v>-0.271384164912539</v>
       </c>
       <c r="JC97" t="n">
-        <v>10.20462154261566</v>
+        <v>7.788480992919941</v>
       </c>
     </row>
     <row r="98">
@@ -78854,10 +78854,10 @@
         <v>0</v>
       </c>
       <c r="JB98" t="n">
-        <v>-0.9291019071641193</v>
+        <v>-0.471384164912539</v>
       </c>
       <c r="JC98" t="n">
-        <v>10.20462165628716</v>
+        <v>7.788481106591447</v>
       </c>
     </row>
     <row r="99">
@@ -79649,10 +79649,10 @@
         <v>0</v>
       </c>
       <c r="JB99" t="n">
-        <v>-0.9291019071641193</v>
+        <v>-0.471384164912539</v>
       </c>
       <c r="JC99" t="n">
-        <v>10.20462167144337</v>
+        <v>7.788481121747648</v>
       </c>
     </row>
     <row r="100">
@@ -80444,10 +80444,10 @@
         <v>0</v>
       </c>
       <c r="JB100" t="n">
-        <v>-0.9291019071641193</v>
+        <v>-0.471384164912539</v>
       </c>
       <c r="JC100" t="n">
-        <v>10.20462143652225</v>
+        <v>7.788480886826536</v>
       </c>
     </row>
     <row r="101">
@@ -81239,10 +81239,10 @@
         <v>0</v>
       </c>
       <c r="JB101" t="n">
-        <v>-0.9291019071641193</v>
+        <v>-0.471384164912539</v>
       </c>
       <c r="JC101" t="n">
-        <v>10.20462149714706</v>
+        <v>7.788480947451339</v>
       </c>
     </row>
     <row r="102">
@@ -82034,10 +82034,10 @@
         <v>0</v>
       </c>
       <c r="JB102" t="n">
-        <v>-0.9291019071641193</v>
+        <v>-0.471384164912539</v>
       </c>
       <c r="JC102" t="n">
-        <v>10.20462136831935</v>
+        <v>7.788480818623632</v>
       </c>
     </row>
     <row r="103">
@@ -82829,10 +82829,10 @@
         <v>0</v>
       </c>
       <c r="JB103" t="n">
-        <v>-0.9291019071641193</v>
+        <v>-0.471384164912539</v>
       </c>
       <c r="JC103" t="n">
-        <v>10.20462150472516</v>
+        <v>7.788480955029439</v>
       </c>
     </row>
     <row r="104">
@@ -83624,10 +83624,10 @@
         <v>0</v>
       </c>
       <c r="JB104" t="n">
-        <v>-0.9291019071641193</v>
+        <v>-0.471384164912539</v>
       </c>
       <c r="JC104" t="n">
-        <v>10.20462167902147</v>
+        <v>7.788481129325747</v>
       </c>
     </row>
     <row r="105">
@@ -84419,10 +84419,10 @@
         <v>0</v>
       </c>
       <c r="JB105" t="n">
-        <v>-0.9291019071641193</v>
+        <v>-0.471384164912539</v>
       </c>
       <c r="JC105" t="n">
-        <v>10.20462182300538</v>
+        <v>7.788481273309656</v>
       </c>
     </row>
     <row r="106">
@@ -85214,10 +85214,10 @@
         <v>0</v>
       </c>
       <c r="JB106" t="n">
-        <v>-0.9291019071641193</v>
+        <v>-0.471384164912539</v>
       </c>
       <c r="JC106" t="n">
-        <v>10.20462165628716</v>
+        <v>7.788481106591447</v>
       </c>
     </row>
     <row r="107">
@@ -86009,10 +86009,10 @@
         <v>0</v>
       </c>
       <c r="JB107" t="n">
-        <v>-0.9291019071641193</v>
+        <v>-0.471384164912539</v>
       </c>
       <c r="JC107" t="n">
-        <v>10.20462164870907</v>
+        <v>7.788481099013347</v>
       </c>
     </row>
     <row r="108">
@@ -86804,10 +86804,10 @@
         <v>0</v>
       </c>
       <c r="JB108" t="n">
-        <v>-0.9291019071641193</v>
+        <v>-0.471384164912539</v>
       </c>
       <c r="JC108" t="n">
-        <v>10.20462136074125</v>
+        <v>7.788480811045531</v>
       </c>
     </row>
     <row r="109">
@@ -87599,10 +87599,10 @@
         <v>0</v>
       </c>
       <c r="JB109" t="n">
-        <v>-0.9291019071641193</v>
+        <v>-0.471384164912539</v>
       </c>
       <c r="JC109" t="n">
-        <v>10.20462137589745</v>
+        <v>7.788480826201732</v>
       </c>
     </row>
     <row r="110">
@@ -88394,10 +88394,10 @@
         <v>0</v>
       </c>
       <c r="JB110" t="n">
-        <v>-0.9291019071641193</v>
+        <v>-0.471384164912539</v>
       </c>
       <c r="JC110" t="n">
-        <v>10.20462160324046</v>
+        <v>7.788481053544745</v>
       </c>
     </row>
     <row r="111">
@@ -89189,10 +89189,10 @@
         <v>0</v>
       </c>
       <c r="JB111" t="n">
-        <v>-0.9291019071641193</v>
+        <v>-0.471384164912539</v>
       </c>
       <c r="JC111" t="n">
-        <v>10.20462158808426</v>
+        <v>7.788481038388543</v>
       </c>
     </row>
     <row r="112">
@@ -89984,10 +89984,10 @@
         <v>0</v>
       </c>
       <c r="JB112" t="n">
-        <v>-0.9291019071641193</v>
+        <v>-0.471384164912539</v>
       </c>
       <c r="JC112" t="n">
-        <v>10.20462169417767</v>
+        <v>7.78848114448195</v>
       </c>
     </row>
     <row r="113">
@@ -90779,10 +90779,10 @@
         <v>0</v>
       </c>
       <c r="JB113" t="n">
-        <v>-0.9291019071641193</v>
+        <v>-0.471384164912539</v>
       </c>
       <c r="JC113" t="n">
-        <v>10.20462142136605</v>
+        <v>7.788480871670334</v>
       </c>
     </row>
     <row r="114">
@@ -91574,10 +91574,10 @@
         <v>0</v>
       </c>
       <c r="JB114" t="n">
-        <v>-0.9291019071641193</v>
+        <v>-0.471384164912539</v>
       </c>
       <c r="JC114" t="n">
-        <v>10.20462151988136</v>
+        <v>7.788480970185639</v>
       </c>
     </row>
     <row r="115">
@@ -92369,10 +92369,10 @@
         <v>0</v>
       </c>
       <c r="JB115" t="n">
-        <v>-0.9291019071641193</v>
+        <v>-0.471384164912539</v>
       </c>
       <c r="JC115" t="n">
-        <v>10.20462167144337</v>
+        <v>7.788481121747648</v>
       </c>
     </row>
     <row r="116">
@@ -93164,10 +93164,10 @@
         <v>0</v>
       </c>
       <c r="JB116" t="n">
-        <v>-0.9291019071641193</v>
+        <v>-0.471384164912539</v>
       </c>
       <c r="JC116" t="n">
-        <v>10.20462168659957</v>
+        <v>7.788481136903848</v>
       </c>
     </row>
     <row r="117">
@@ -93959,10 +93959,10 @@
         <v>0</v>
       </c>
       <c r="JB117" t="n">
-        <v>-0.9291019071641193</v>
+        <v>-0.471384164912539</v>
       </c>
       <c r="JC117" t="n">
-        <v>10.20462166386527</v>
+        <v>7.788481114169548</v>
       </c>
     </row>
     <row r="118">
@@ -94754,10 +94754,10 @@
         <v>0</v>
       </c>
       <c r="JB118" t="n">
-        <v>-0.9291019071641193</v>
+        <v>-0.471384164912539</v>
       </c>
       <c r="JC118" t="n">
-        <v>10.20462174722437</v>
+        <v>7.788481197528651</v>
       </c>
     </row>
     <row r="119">
@@ -95549,10 +95549,10 @@
         <v>0</v>
       </c>
       <c r="JB119" t="n">
-        <v>-0.9291019071641193</v>
+        <v>-0.471384164912539</v>
       </c>
       <c r="JC119" t="n">
-        <v>10.20462184573968</v>
+        <v>7.788481296043956</v>
       </c>
     </row>
     <row r="120">
@@ -96344,10 +96344,10 @@
         <v>0</v>
       </c>
       <c r="JB120" t="n">
-        <v>-0.9291019071641193</v>
+        <v>-0.471384164912539</v>
       </c>
       <c r="JC120" t="n">
-        <v>10.20462167902147</v>
+        <v>7.788481129325747</v>
       </c>
     </row>
     <row r="121">
@@ -97139,10 +97139,10 @@
         <v>0</v>
       </c>
       <c r="JB121" t="n">
-        <v>-0.9291019071641193</v>
+        <v>-0.471384164912539</v>
       </c>
       <c r="JC121" t="n">
-        <v>10.20462166386527</v>
+        <v>7.788481114169548</v>
       </c>
     </row>
     <row r="122">
@@ -97934,10 +97934,10 @@
         <v>0</v>
       </c>
       <c r="JB122" t="n">
-        <v>-0.9291019071641193</v>
+        <v>-0.471384164912539</v>
       </c>
       <c r="JC122" t="n">
-        <v>10.20462163355286</v>
+        <v>7.788481083857145</v>
       </c>
     </row>
     <row r="123">
@@ -98729,10 +98729,10 @@
         <v>0</v>
       </c>
       <c r="JB123" t="n">
-        <v>-0.9291019071641193</v>
+        <v>-0.471384164912539</v>
       </c>
       <c r="JC123" t="n">
-        <v>10.20462161839666</v>
+        <v>7.788481068700945</v>
       </c>
     </row>
     <row r="124">
@@ -99524,10 +99524,10 @@
         <v>0</v>
       </c>
       <c r="JB124" t="n">
-        <v>-0.9291019071641193</v>
+        <v>-0.471384164912539</v>
       </c>
       <c r="JC124" t="n">
-        <v>10.20462165628716</v>
+        <v>7.788481106591447</v>
       </c>
     </row>
     <row r="125">
@@ -100319,10 +100319,10 @@
         <v>0</v>
       </c>
       <c r="JB125" t="n">
-        <v>-0.9291019071641193</v>
+        <v>-0.471384164912539</v>
       </c>
       <c r="JC125" t="n">
-        <v>10.20462167144337</v>
+        <v>7.788481121747648</v>
       </c>
     </row>
     <row r="126">
@@ -101114,10 +101114,10 @@
         <v>0</v>
       </c>
       <c r="JB126" t="n">
-        <v>-0.9291019071641193</v>
+        <v>-0.471384164912539</v>
       </c>
       <c r="JC126" t="n">
-        <v>10.20462166386527</v>
+        <v>7.788481114169548</v>
       </c>
     </row>
   </sheetData>

--- a/out/MLP-S4_repeat_2_000007.xlsx
+++ b/out/MLP-S4_repeat_2_000007.xlsx
@@ -1731,12 +1731,12 @@
       </c>
       <c r="JA1" s="1" t="inlineStr">
         <is>
-          <t>Predicted Value</t>
+          <t>Original Prediction</t>
         </is>
       </c>
       <c r="JB1" s="1" t="inlineStr">
         <is>
-          <t>Enhanced Signal</t>
+          <t>Trading Signal</t>
         </is>
       </c>
       <c r="JC1" s="1" t="inlineStr">
@@ -2531,10 +2531,10 @@
         </is>
       </c>
       <c r="JA2" t="n">
-        <v>0</v>
+        <v>0.4045032560825348</v>
       </c>
       <c r="JB2" t="n">
-        <v>-0.471384164912539</v>
+        <v>-1.28</v>
       </c>
       <c r="JC2" t="n">
         <v>0</v>
@@ -3326,10 +3326,10 @@
         </is>
       </c>
       <c r="JA3" t="n">
-        <v>0</v>
+        <v>0.4116416871547699</v>
       </c>
       <c r="JB3" t="n">
-        <v>-0.471384164912539</v>
+        <v>-0.8599999999999997</v>
       </c>
       <c r="JC3" t="n">
         <v>0</v>
@@ -4117,14 +4117,14 @@
       </c>
       <c r="IZ4" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA4" t="n">
-        <v>0</v>
+        <v>0.4008882641792297</v>
       </c>
       <c r="JB4" t="n">
-        <v>0.3845367972155144</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC4" t="n">
         <v>0</v>
@@ -4912,14 +4912,14 @@
       </c>
       <c r="IZ5" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA5" t="n">
-        <v>1</v>
+        <v>0.5511902570724487</v>
       </c>
       <c r="JB5" t="n">
-        <v>0.5845367972155144</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC5" t="n">
         <v>0</v>
@@ -5711,10 +5711,10 @@
         </is>
       </c>
       <c r="JA6" t="n">
-        <v>0</v>
+        <v>0.4747338593006134</v>
       </c>
       <c r="JB6" t="n">
-        <v>0.5845367972155144</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC6" t="n">
         <v>0</v>
@@ -6506,10 +6506,10 @@
         </is>
       </c>
       <c r="JA7" t="n">
-        <v>0</v>
+        <v>0.4231065213680267</v>
       </c>
       <c r="JB7" t="n">
-        <v>-0.271384164912539</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC7" t="n">
         <v>0</v>
@@ -7301,10 +7301,10 @@
         </is>
       </c>
       <c r="JA8" t="n">
-        <v>0</v>
+        <v>0.3929059207439423</v>
       </c>
       <c r="JB8" t="n">
-        <v>-0.471384164912539</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC8" t="n">
         <v>0</v>
@@ -8096,10 +8096,10 @@
         </is>
       </c>
       <c r="JA9" t="n">
-        <v>0</v>
+        <v>0.411174863576889</v>
       </c>
       <c r="JB9" t="n">
-        <v>-0.471384164912539</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC9" t="n">
         <v>0</v>
@@ -8891,10 +8891,10 @@
         </is>
       </c>
       <c r="JA10" t="n">
-        <v>0</v>
+        <v>0.4138774871826172</v>
       </c>
       <c r="JB10" t="n">
-        <v>-0.471384164912539</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC10" t="n">
         <v>0</v>
@@ -9686,10 +9686,10 @@
         </is>
       </c>
       <c r="JA11" t="n">
-        <v>0</v>
+        <v>0.4155213534832001</v>
       </c>
       <c r="JB11" t="n">
-        <v>-0.471384164912539</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC11" t="n">
         <v>0</v>
@@ -10481,10 +10481,10 @@
         </is>
       </c>
       <c r="JA12" t="n">
-        <v>0</v>
+        <v>0.4008760154247284</v>
       </c>
       <c r="JB12" t="n">
-        <v>-0.471384164912539</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC12" t="n">
         <v>0</v>
@@ -11276,10 +11276,10 @@
         </is>
       </c>
       <c r="JA13" t="n">
-        <v>0</v>
+        <v>0.3953934907913208</v>
       </c>
       <c r="JB13" t="n">
-        <v>-0.471384164912539</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC13" t="n">
         <v>0</v>
@@ -12071,10 +12071,10 @@
         </is>
       </c>
       <c r="JA14" t="n">
-        <v>0</v>
+        <v>0.4228793680667877</v>
       </c>
       <c r="JB14" t="n">
-        <v>-0.471384164912539</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC14" t="n">
         <v>0</v>
@@ -12866,10 +12866,10 @@
         </is>
       </c>
       <c r="JA15" t="n">
-        <v>0</v>
+        <v>0.4200739562511444</v>
       </c>
       <c r="JB15" t="n">
-        <v>-0.471384164912539</v>
+        <v>0.02000000000000007</v>
       </c>
       <c r="JC15" t="n">
         <v>0</v>
@@ -13661,10 +13661,10 @@
         </is>
       </c>
       <c r="JA16" t="n">
-        <v>0</v>
+        <v>0.4503850042819977</v>
       </c>
       <c r="JB16" t="n">
-        <v>-0.471384164912539</v>
+        <v>0.1600000000000001</v>
       </c>
       <c r="JC16" t="n">
         <v>0</v>
@@ -14456,10 +14456,10 @@
         </is>
       </c>
       <c r="JA17" t="n">
-        <v>0</v>
+        <v>0.4215535819530487</v>
       </c>
       <c r="JB17" t="n">
-        <v>-0.471384164912539</v>
+        <v>0.16</v>
       </c>
       <c r="JC17" t="n">
         <v>0</v>
@@ -15251,10 +15251,10 @@
         </is>
       </c>
       <c r="JA18" t="n">
-        <v>0</v>
+        <v>0.4238715171813965</v>
       </c>
       <c r="JB18" t="n">
-        <v>-0.471384164912539</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC18" t="n">
         <v>0</v>
@@ -16046,10 +16046,10 @@
         </is>
       </c>
       <c r="JA19" t="n">
-        <v>0</v>
+        <v>0.4082376956939697</v>
       </c>
       <c r="JB19" t="n">
-        <v>-0.471384164912539</v>
+        <v>0.3</v>
       </c>
       <c r="JC19" t="n">
         <v>0</v>
@@ -16841,10 +16841,10 @@
         </is>
       </c>
       <c r="JA20" t="n">
-        <v>0</v>
+        <v>0.4400605857372284</v>
       </c>
       <c r="JB20" t="n">
-        <v>-0.471384164912539</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC20" t="n">
         <v>0</v>
@@ -17636,10 +17636,10 @@
         </is>
       </c>
       <c r="JA21" t="n">
-        <v>0</v>
+        <v>0.4438421726226807</v>
       </c>
       <c r="JB21" t="n">
-        <v>-0.471384164912539</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC21" t="n">
         <v>0</v>
@@ -18431,10 +18431,10 @@
         </is>
       </c>
       <c r="JA22" t="n">
-        <v>0</v>
+        <v>0.4768856167793274</v>
       </c>
       <c r="JB22" t="n">
-        <v>0.5845367972155144</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC22" t="n">
         <v>0</v>
@@ -19226,10 +19226,10 @@
         </is>
       </c>
       <c r="JA23" t="n">
-        <v>1</v>
+        <v>0.5426238179206848</v>
       </c>
       <c r="JB23" t="n">
-        <v>0.5845367972155144</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC23" t="n">
         <v>0</v>
@@ -20021,10 +20021,10 @@
         </is>
       </c>
       <c r="JA24" t="n">
-        <v>0</v>
+        <v>0.4832577407360077</v>
       </c>
       <c r="JB24" t="n">
-        <v>0.5845367972155144</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC24" t="n">
         <v>0</v>
@@ -20816,10 +20816,10 @@
         </is>
       </c>
       <c r="JA25" t="n">
-        <v>0</v>
+        <v>0.4559786319732666</v>
       </c>
       <c r="JB25" t="n">
-        <v>-0.271384164912539</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC25" t="n">
         <v>0</v>
@@ -21611,10 +21611,10 @@
         </is>
       </c>
       <c r="JA26" t="n">
-        <v>0</v>
+        <v>0.4418408274650574</v>
       </c>
       <c r="JB26" t="n">
-        <v>-0.271384164912539</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC26" t="n">
         <v>0</v>
@@ -22406,10 +22406,10 @@
         </is>
       </c>
       <c r="JA27" t="n">
-        <v>0</v>
+        <v>0.4338961541652679</v>
       </c>
       <c r="JB27" t="n">
-        <v>-0.471384164912539</v>
+        <v>-0.3</v>
       </c>
       <c r="JC27" t="n">
         <v>0</v>
@@ -23201,10 +23201,10 @@
         </is>
       </c>
       <c r="JA28" t="n">
-        <v>0</v>
+        <v>0.4210349321365356</v>
       </c>
       <c r="JB28" t="n">
-        <v>-0.471384164912539</v>
+        <v>-0.3</v>
       </c>
       <c r="JC28" t="n">
         <v>0</v>
@@ -23996,10 +23996,10 @@
         </is>
       </c>
       <c r="JA29" t="n">
-        <v>0</v>
+        <v>0.4702668488025665</v>
       </c>
       <c r="JB29" t="n">
-        <v>-0.471384164912539</v>
+        <v>-0.16</v>
       </c>
       <c r="JC29" t="n">
         <v>0</v>
@@ -24791,10 +24791,10 @@
         </is>
       </c>
       <c r="JA30" t="n">
-        <v>0</v>
+        <v>0.4648931324481964</v>
       </c>
       <c r="JB30" t="n">
-        <v>-0.471384164912539</v>
+        <v>-0.16</v>
       </c>
       <c r="JC30" t="n">
         <v>0</v>
@@ -25586,10 +25586,10 @@
         </is>
       </c>
       <c r="JA31" t="n">
-        <v>0</v>
+        <v>0.4497069120407104</v>
       </c>
       <c r="JB31" t="n">
-        <v>-0.471384164912539</v>
+        <v>-0.16</v>
       </c>
       <c r="JC31" t="n">
         <v>0</v>
@@ -26381,10 +26381,10 @@
         </is>
       </c>
       <c r="JA32" t="n">
-        <v>0</v>
+        <v>0.4389671683311462</v>
       </c>
       <c r="JB32" t="n">
-        <v>-0.471384164912539</v>
+        <v>-0.16</v>
       </c>
       <c r="JC32" t="n">
         <v>0</v>
@@ -27176,10 +27176,10 @@
         </is>
       </c>
       <c r="JA33" t="n">
-        <v>0</v>
+        <v>0.4340663254261017</v>
       </c>
       <c r="JB33" t="n">
-        <v>-0.471384164912539</v>
+        <v>-0.3</v>
       </c>
       <c r="JC33" t="n">
         <v>0</v>
@@ -27971,10 +27971,10 @@
         </is>
       </c>
       <c r="JA34" t="n">
-        <v>0</v>
+        <v>0.439145565032959</v>
       </c>
       <c r="JB34" t="n">
-        <v>-0.471384164912539</v>
+        <v>-0.3</v>
       </c>
       <c r="JC34" t="n">
         <v>0</v>
@@ -28766,10 +28766,10 @@
         </is>
       </c>
       <c r="JA35" t="n">
-        <v>0</v>
+        <v>0.4480175971984863</v>
       </c>
       <c r="JB35" t="n">
-        <v>0.5845367972155144</v>
+        <v>-0.16</v>
       </c>
       <c r="JC35" t="n">
         <v>0</v>
@@ -29561,10 +29561,10 @@
         </is>
       </c>
       <c r="JA36" t="n">
-        <v>1</v>
+        <v>0.5353362560272217</v>
       </c>
       <c r="JB36" t="n">
-        <v>1.440457759343568</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC36" t="n">
         <v>0</v>
@@ -30356,10 +30356,10 @@
         </is>
       </c>
       <c r="JA37" t="n">
-        <v>1</v>
+        <v>0.7064709067344666</v>
       </c>
       <c r="JB37" t="n">
-        <v>2.296378721471621</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC37" t="n">
         <v>0</v>
@@ -31151,10 +31151,10 @@
         </is>
       </c>
       <c r="JA38" t="n">
-        <v>1</v>
+        <v>0.6145474910736084</v>
       </c>
       <c r="JB38" t="n">
-        <v>2.296378721471621</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC38" t="n">
         <v>0</v>
@@ -31946,13 +31946,13 @@
         </is>
       </c>
       <c r="JA39" t="n">
-        <v>1</v>
+        <v>0.5793716907501221</v>
       </c>
       <c r="JB39" t="n">
-        <v>2.296378721471621</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC39" t="n">
-        <v>-0.0002751175154725788</v>
+        <v>-0.0001762581139509566</v>
       </c>
     </row>
     <row r="40">
@@ -32733,7 +32733,7 @@
         <v>0</v>
       </c>
       <c r="IY40" t="n">
-        <v>3.171698555222005</v>
+        <v>2.031995661651695</v>
       </c>
       <c r="IZ40" t="inlineStr">
         <is>
@@ -32741,13 +32741,13 @@
         </is>
       </c>
       <c r="JA40" t="n">
-        <v>1</v>
+        <v>0.5745025873184204</v>
       </c>
       <c r="JB40" t="n">
-        <v>2.296378721471621</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC40" t="n">
-        <v>6.348300135573369</v>
+        <v>4.067132573440041</v>
       </c>
     </row>
     <row r="41">
@@ -33528,7 +33528,7 @@
         <v>0</v>
       </c>
       <c r="IY41" t="n">
-        <v>0.4756103692814754</v>
+        <v>0.304706836431729</v>
       </c>
       <c r="IZ41" t="inlineStr">
         <is>
@@ -33536,13 +33536,13 @@
         </is>
       </c>
       <c r="JA41" t="n">
-        <v>1</v>
+        <v>0.5475561022758484</v>
       </c>
       <c r="JB41" t="n">
-        <v>2.296378721471621</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC41" t="n">
-        <v>4.12356531166803</v>
+        <v>2.641823215454815</v>
       </c>
     </row>
     <row r="42">
@@ -34323,7 +34323,7 @@
         <v>0</v>
       </c>
       <c r="IY42" t="n">
-        <v>0.5946677152079944</v>
+        <v>0.3809826339917982</v>
       </c>
       <c r="IZ42" t="inlineStr">
         <is>
@@ -34331,13 +34331,13 @@
         </is>
       </c>
       <c r="JA42" t="n">
-        <v>1</v>
+        <v>0.5233437418937683</v>
       </c>
       <c r="JB42" t="n">
-        <v>2.296378721471621</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC42" t="n">
-        <v>4.837365903046035</v>
+        <v>3.099130150153705</v>
       </c>
     </row>
     <row r="43">
@@ -35118,7 +35118,7 @@
         <v>0</v>
       </c>
       <c r="IY43" t="n">
-        <v>0.8524533495975014</v>
+        <v>0.5461367990545677</v>
       </c>
       <c r="IZ43" t="inlineStr">
         <is>
@@ -35126,13 +35126,13 @@
         </is>
       </c>
       <c r="JA43" t="n">
-        <v>1</v>
+        <v>0.6155257225036621</v>
       </c>
       <c r="JB43" t="n">
-        <v>2.296378721471621</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC43" t="n">
-        <v>5.947940484345215</v>
+        <v>3.810636331820818</v>
       </c>
     </row>
     <row r="44">
@@ -35913,7 +35913,7 @@
         <v>0</v>
       </c>
       <c r="IY44" t="n">
-        <v>0.9119558822331834</v>
+        <v>0.5842581963286199</v>
       </c>
       <c r="IZ44" t="inlineStr">
         <is>
@@ -35921,13 +35921,13 @@
         </is>
       </c>
       <c r="JA44" t="n">
-        <v>1</v>
+        <v>0.6625873446464539</v>
       </c>
       <c r="JB44" t="n">
-        <v>2.296378721471621</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC44" t="n">
-        <v>6.91946315325602</v>
+        <v>4.43305701572845</v>
       </c>
     </row>
     <row r="45">
@@ -36708,7 +36708,7 @@
         <v>0</v>
       </c>
       <c r="IY45" t="n">
-        <v>0.9664894219458098</v>
+        <v>0.619196663161341</v>
       </c>
       <c r="IZ45" t="inlineStr">
         <is>
@@ -36716,13 +36716,13 @@
         </is>
       </c>
       <c r="JA45" t="n">
-        <v>1</v>
+        <v>0.7246213555335999</v>
       </c>
       <c r="JB45" t="n">
-        <v>2.296378721471621</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC45" t="n">
-        <v>7.94055590315098</v>
+        <v>5.087235660467096</v>
       </c>
     </row>
     <row r="46">
@@ -37503,7 +37503,7 @@
         <v>0</v>
       </c>
       <c r="IY46" t="n">
-        <v>0.4361587006051614</v>
+        <v>0.2794319377854967</v>
       </c>
       <c r="IZ46" t="inlineStr">
         <is>
@@ -37511,13 +37511,13 @@
         </is>
       </c>
       <c r="JA46" t="n">
-        <v>1</v>
+        <v>0.7824833393096924</v>
       </c>
       <c r="JB46" t="n">
-        <v>2.096378721471621</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC46" t="n">
-        <v>7.845580589561809</v>
+        <v>5.026388322909726</v>
       </c>
     </row>
     <row r="47">
@@ -38298,7 +38298,7 @@
         <v>0</v>
       </c>
       <c r="IY47" t="n">
-        <v>0.2106447170866213</v>
+        <v>0.1349522109205024</v>
       </c>
       <c r="IZ47" t="inlineStr">
         <is>
@@ -38306,13 +38306,13 @@
         </is>
       </c>
       <c r="JA47" t="n">
-        <v>1</v>
+        <v>0.5264084935188293</v>
       </c>
       <c r="JB47" t="n">
-        <v>2.096378721471621</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC47" t="n">
-        <v>7.83036926964175</v>
+        <v>5.016642981444461</v>
       </c>
     </row>
     <row r="48">
@@ -39093,7 +39093,7 @@
         <v>0</v>
       </c>
       <c r="IY48" t="n">
-        <v>0.1003665492948865</v>
+        <v>0.06430132361609035</v>
       </c>
       <c r="IZ48" t="inlineStr">
         <is>
@@ -39101,13 +39101,13 @@
         </is>
       </c>
       <c r="JA48" t="n">
-        <v>1</v>
+        <v>0.6250103116035461</v>
       </c>
       <c r="JB48" t="n">
-        <v>1.240457759343568</v>
+        <v>-0.16</v>
       </c>
       <c r="JC48" t="n">
-        <v>7.820289082689608</v>
+        <v>5.010184959644628</v>
       </c>
     </row>
     <row r="49">
@@ -39888,7 +39888,7 @@
         <v>0</v>
       </c>
       <c r="IY49" t="n">
-        <v>0.02973754525910433</v>
+        <v>0.01905167046229239</v>
       </c>
       <c r="IZ49" t="inlineStr">
         <is>
@@ -39896,13 +39896,13 @@
         </is>
       </c>
       <c r="JA49" t="n">
-        <v>0</v>
+        <v>0.4772276282310486</v>
       </c>
       <c r="JB49" t="n">
-        <v>0.3845367972155144</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC49" t="n">
-        <v>7.77929144151685</v>
+        <v>4.983919210836554</v>
       </c>
     </row>
     <row r="50">
@@ -40683,7 +40683,7 @@
         <v>0</v>
       </c>
       <c r="IY50" t="n">
-        <v>0.01967075773815177</v>
+        <v>0.01260080754943257</v>
       </c>
       <c r="IZ50" t="inlineStr">
         <is>
@@ -40691,13 +40691,13 @@
         </is>
       </c>
       <c r="JA50" t="n">
-        <v>0</v>
+        <v>0.4795134365558624</v>
       </c>
       <c r="JB50" t="n">
-        <v>-0.471384164912539</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC50" t="n">
-        <v>7.788879157773713</v>
+        <v>4.990060604748933</v>
       </c>
     </row>
     <row r="51">
@@ -41478,7 +41478,7 @@
         <v>0</v>
       </c>
       <c r="IY51" t="n">
-        <v>0.01006578062694764</v>
+        <v>0.00644679370502156</v>
       </c>
       <c r="IZ51" t="inlineStr">
         <is>
@@ -41486,13 +41486,13 @@
         </is>
       </c>
       <c r="JA51" t="n">
-        <v>0</v>
+        <v>0.4119186401367188</v>
       </c>
       <c r="JB51" t="n">
-        <v>-0.471384164912539</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC51" t="n">
-        <v>7.789327268064661</v>
+        <v>4.990345910255853</v>
       </c>
     </row>
     <row r="52">
@@ -42273,7 +42273,7 @@
         <v>0</v>
       </c>
       <c r="IY52" t="n">
-        <v>0.005146090157384079</v>
+        <v>0.003295845148732146</v>
       </c>
       <c r="IZ52" t="inlineStr">
         <is>
@@ -42281,13 +42281,13 @@
         </is>
       </c>
       <c r="JA52" t="n">
-        <v>0</v>
+        <v>0.4276770353317261</v>
       </c>
       <c r="JB52" t="n">
-        <v>-0.471384164912539</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC52" t="n">
-        <v>7.789548684211398</v>
+        <v>4.990485984322567</v>
       </c>
     </row>
     <row r="53">
@@ -43068,7 +43068,7 @@
         <v>0</v>
       </c>
       <c r="IY53" t="n">
-        <v>0.001931868503071262</v>
+        <v>0.001235534379262914</v>
       </c>
       <c r="IZ53" t="inlineStr">
         <is>
@@ -43076,13 +43076,13 @@
         </is>
       </c>
       <c r="JA53" t="n">
-        <v>0</v>
+        <v>0.4154200255870819</v>
       </c>
       <c r="JB53" t="n">
-        <v>-0.471384164912539</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC53" t="n">
-        <v>7.788261421135045</v>
+        <v>4.9896594645375</v>
       </c>
     </row>
     <row r="54">
@@ -43863,7 +43863,7 @@
         <v>0</v>
       </c>
       <c r="IY54" t="n">
-        <v>0.001050182644913753</v>
+        <v>0.0006715049013520539</v>
       </c>
       <c r="IZ54" t="inlineStr">
         <is>
@@ -43871,13 +43871,13 @@
         </is>
       </c>
       <c r="JA54" t="n">
-        <v>0</v>
+        <v>0.3852797150611877</v>
       </c>
       <c r="JB54" t="n">
-        <v>-0.471384164912539</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC54" t="n">
-        <v>7.788429664455926</v>
+        <v>4.989765491587336</v>
       </c>
     </row>
     <row r="55">
@@ -44658,7 +44658,7 @@
         <v>0</v>
       </c>
       <c r="IY55" t="n">
-        <v>0.0005036271683573302</v>
+        <v>0.0003208392797289147</v>
       </c>
       <c r="IZ55" t="inlineStr">
         <is>
@@ -44666,13 +44666,13 @@
         </is>
       </c>
       <c r="JA55" t="n">
-        <v>0</v>
+        <v>0.3778193295001984</v>
       </c>
       <c r="JB55" t="n">
-        <v>-0.471384164912539</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC55" t="n">
-        <v>7.788385243403678</v>
+        <v>4.98973523747574</v>
       </c>
     </row>
     <row r="56">
@@ -45453,7 +45453,7 @@
         <v>0</v>
       </c>
       <c r="IY56" t="n">
-        <v>0.0003098656375792129</v>
+        <v>0.0001967107990741833</v>
       </c>
       <c r="IZ56" t="inlineStr">
         <is>
@@ -45461,13 +45461,13 @@
         </is>
       </c>
       <c r="JA56" t="n">
-        <v>0</v>
+        <v>0.4141634702682495</v>
       </c>
       <c r="JB56" t="n">
-        <v>-0.471384164912539</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC56" t="n">
-        <v>7.788501109671133</v>
+        <v>4.989807667428328</v>
       </c>
     </row>
     <row r="57">
@@ -46248,7 +46248,7 @@
         <v>0</v>
       </c>
       <c r="IY57" t="n">
-        <v>0.0001596990651976723</v>
+        <v>9.999565406351607e-05</v>
       </c>
       <c r="IZ57" t="inlineStr">
         <is>
@@ -46256,13 +46256,13 @@
         </is>
       </c>
       <c r="JA57" t="n">
-        <v>0</v>
+        <v>0.3504213690757751</v>
       </c>
       <c r="JB57" t="n">
-        <v>0.3845367972155144</v>
+        <v>0.16</v>
       </c>
       <c r="JC57" t="n">
-        <v>7.788510459224481</v>
+        <v>4.98981186073719</v>
       </c>
     </row>
     <row r="58">
@@ -47043,7 +47043,7 @@
         <v>0</v>
       </c>
       <c r="IY58" t="n">
-        <v>7.492745046281422e-05</v>
+        <v>4.595374967004406e-05</v>
       </c>
       <c r="IZ58" t="inlineStr">
         <is>
@@ -47051,13 +47051,13 @@
         </is>
       </c>
       <c r="JA58" t="n">
-        <v>1</v>
+        <v>0.6651333570480347</v>
       </c>
       <c r="JB58" t="n">
-        <v>1.440457759343568</v>
+        <v>0.1600000000000001</v>
       </c>
       <c r="JC58" t="n">
-        <v>7.788500511950513</v>
+        <v>4.989803676537635</v>
       </c>
     </row>
     <row r="59">
@@ -47838,7 +47838,7 @@
         <v>0</v>
       </c>
       <c r="IY59" t="n">
-        <v>4.616585511050847e-05</v>
+        <v>2.82578058218305e-05</v>
       </c>
       <c r="IZ59" t="inlineStr">
         <is>
@@ -47846,13 +47846,13 @@
         </is>
       </c>
       <c r="JA59" t="n">
-        <v>1</v>
+        <v>0.5251737236976624</v>
       </c>
       <c r="JB59" t="n">
-        <v>1.440457759343568</v>
+        <v>0.1600000000000001</v>
       </c>
       <c r="JC59" t="n">
-        <v>7.788517881024123</v>
+        <v>4.989813216435479</v>
       </c>
     </row>
     <row r="60">
@@ -48633,7 +48633,7 @@
         <v>0</v>
       </c>
       <c r="IY60" t="n">
-        <v>1.831222555273368e-05</v>
+        <v>1.015294660927689e-05</v>
       </c>
       <c r="IZ60" t="inlineStr">
         <is>
@@ -48641,13 +48641,13 @@
         </is>
       </c>
       <c r="JA60" t="n">
-        <v>0</v>
+        <v>0.3761074542999268</v>
       </c>
       <c r="JB60" t="n">
-        <v>0.5845367972155144</v>
+        <v>0.16</v>
       </c>
       <c r="JC60" t="n">
-        <v>7.78850830584022</v>
+        <v>4.989805242565942</v>
       </c>
     </row>
     <row r="61">
@@ -49428,7 +49428,7 @@
         <v>0</v>
       </c>
       <c r="IY61" t="n">
-        <v>5.293691574854516e-06</v>
+        <v>1.176214944912711e-06</v>
       </c>
       <c r="IZ61" t="inlineStr">
         <is>
@@ -49436,13 +49436,13 @@
         </is>
       </c>
       <c r="JA61" t="n">
-        <v>0</v>
+        <v>0.3653608858585358</v>
       </c>
       <c r="JB61" t="n">
-        <v>-0.271384164912539</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC61" t="n">
-        <v>7.788500565199114</v>
+        <v>4.989798461775472</v>
       </c>
     </row>
     <row r="62">
@@ -50223,7 +50223,7 @@
         <v>0</v>
       </c>
       <c r="IY62" t="n">
-        <v>5.63141154556023e-07</v>
+        <v>-1.662115307266386e-06</v>
       </c>
       <c r="IZ62" t="inlineStr">
         <is>
@@ -50231,13 +50231,13 @@
         </is>
       </c>
       <c r="JA62" t="n">
-        <v>0</v>
+        <v>0.3584780395030975</v>
       </c>
       <c r="JB62" t="n">
-        <v>-0.471384164912539</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC62" t="n">
-        <v>7.788496392027522</v>
+        <v>4.989794041231621</v>
       </c>
     </row>
     <row r="63">
@@ -51026,13 +51026,13 @@
         </is>
       </c>
       <c r="JA63" t="n">
-        <v>0</v>
+        <v>0.3962843716144562</v>
       </c>
       <c r="JB63" t="n">
-        <v>-0.471384164912539</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC63" t="n">
-        <v>7.788490669748491</v>
+        <v>4.989788462936497</v>
       </c>
     </row>
     <row r="64">
@@ -51821,13 +51821,13 @@
         </is>
       </c>
       <c r="JA64" t="n">
-        <v>0</v>
+        <v>0.4608432948589325</v>
       </c>
       <c r="JB64" t="n">
-        <v>0.3845367972155144</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC64" t="n">
-        <v>7.788485600393122</v>
+        <v>4.98978341631543</v>
       </c>
     </row>
     <row r="65">
@@ -52608,7 +52608,7 @@
         <v>0</v>
       </c>
       <c r="IY65" t="n">
-        <v>-3.735991635587426e-06</v>
+        <v>0</v>
       </c>
       <c r="IZ65" t="inlineStr">
         <is>
@@ -52616,13 +52616,13 @@
         </is>
       </c>
       <c r="JA65" t="n">
-        <v>1</v>
+        <v>0.6227206587791443</v>
       </c>
       <c r="JB65" t="n">
-        <v>1.440457759343568</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC65" t="n">
-        <v>7.788481235419154</v>
+        <v>4.989783734595646</v>
       </c>
     </row>
     <row r="66">
@@ -53411,13 +53411,13 @@
         </is>
       </c>
       <c r="JA66" t="n">
-        <v>1</v>
+        <v>0.9041013121604919</v>
       </c>
       <c r="JB66" t="n">
-        <v>2.296378721471621</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC66" t="n">
-        <v>7.78848232666561</v>
+        <v>4.989784825842103</v>
       </c>
     </row>
     <row r="67">
@@ -54206,13 +54206,13 @@
         </is>
       </c>
       <c r="JA67" t="n">
-        <v>1</v>
+        <v>0.6969496011734009</v>
       </c>
       <c r="JB67" t="n">
-        <v>1.440457759343568</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC67" t="n">
-        <v>7.788481637058474</v>
+        <v>4.989784136234967</v>
       </c>
     </row>
     <row r="68">
@@ -55001,13 +55001,13 @@
         </is>
       </c>
       <c r="JA68" t="n">
-        <v>0</v>
+        <v>0.4800566732883453</v>
       </c>
       <c r="JB68" t="n">
-        <v>0.5845367972155144</v>
+        <v>0.16</v>
       </c>
       <c r="JC68" t="n">
-        <v>7.788481667370876</v>
+        <v>4.989784166547369</v>
       </c>
     </row>
     <row r="69">
@@ -55796,13 +55796,13 @@
         </is>
       </c>
       <c r="JA69" t="n">
-        <v>0</v>
+        <v>0.4182166159152985</v>
       </c>
       <c r="JB69" t="n">
-        <v>-0.471384164912539</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC69" t="n">
-        <v>7.788481477918366</v>
+        <v>4.989783977094859</v>
       </c>
     </row>
     <row r="70">
@@ -56591,13 +56591,13 @@
         </is>
       </c>
       <c r="JA70" t="n">
-        <v>0</v>
+        <v>0.414066880941391</v>
       </c>
       <c r="JB70" t="n">
-        <v>-0.471384164912539</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC70" t="n">
-        <v>7.788481530965069</v>
+        <v>4.989784030141562</v>
       </c>
     </row>
     <row r="71">
@@ -57386,13 +57386,13 @@
         </is>
       </c>
       <c r="JA71" t="n">
-        <v>0</v>
+        <v>0.3641100525856018</v>
       </c>
       <c r="JB71" t="n">
-        <v>-0.471384164912539</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC71" t="n">
-        <v>7.78848158401177</v>
+        <v>4.989784083188264</v>
       </c>
     </row>
     <row r="72">
@@ -58181,13 +58181,13 @@
         </is>
       </c>
       <c r="JA72" t="n">
-        <v>0</v>
+        <v>0.3118339776992798</v>
       </c>
       <c r="JB72" t="n">
-        <v>-0.471384164912539</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC72" t="n">
-        <v>7.788481546121269</v>
+        <v>4.989784045297762</v>
       </c>
     </row>
     <row r="73">
@@ -58976,13 +58976,13 @@
         </is>
       </c>
       <c r="JA73" t="n">
-        <v>0</v>
+        <v>0.2962372899055481</v>
       </c>
       <c r="JB73" t="n">
-        <v>-0.471384164912539</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC73" t="n">
-        <v>7.788481417293563</v>
+        <v>4.989783916470055</v>
       </c>
     </row>
     <row r="74">
@@ -59771,13 +59771,13 @@
         </is>
       </c>
       <c r="JA74" t="n">
-        <v>0</v>
+        <v>0.3054482042789459</v>
       </c>
       <c r="JB74" t="n">
-        <v>-0.471384164912539</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC74" t="n">
-        <v>7.788481273309656</v>
+        <v>4.989783772486148</v>
       </c>
     </row>
     <row r="75">
@@ -60566,13 +60566,13 @@
         </is>
       </c>
       <c r="JA75" t="n">
-        <v>0</v>
+        <v>0.2885632812976837</v>
       </c>
       <c r="JB75" t="n">
-        <v>-0.471384164912539</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC75" t="n">
-        <v>7.788481114169548</v>
+        <v>4.98978361334604</v>
       </c>
     </row>
     <row r="76">
@@ -61361,13 +61361,13 @@
         </is>
       </c>
       <c r="JA76" t="n">
-        <v>0</v>
+        <v>0.3279168307781219</v>
       </c>
       <c r="JB76" t="n">
-        <v>-0.471384164912539</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC76" t="n">
-        <v>7.788481167216251</v>
+        <v>4.989783666392743</v>
       </c>
     </row>
     <row r="77">
@@ -62156,13 +62156,13 @@
         </is>
       </c>
       <c r="JA77" t="n">
-        <v>0</v>
+        <v>0.3180650770664215</v>
       </c>
       <c r="JB77" t="n">
-        <v>-0.471384164912539</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC77" t="n">
-        <v>7.788481114169548</v>
+        <v>4.98978361334604</v>
       </c>
     </row>
     <row r="78">
@@ -62951,13 +62951,13 @@
         </is>
       </c>
       <c r="JA78" t="n">
-        <v>0</v>
+        <v>0.3609218597412109</v>
       </c>
       <c r="JB78" t="n">
-        <v>-0.471384164912539</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC78" t="n">
-        <v>7.788481114169548</v>
+        <v>4.98978361334604</v>
       </c>
     </row>
     <row r="79">
@@ -63746,13 +63746,13 @@
         </is>
       </c>
       <c r="JA79" t="n">
-        <v>0</v>
+        <v>0.3800865411758423</v>
       </c>
       <c r="JB79" t="n">
-        <v>-0.471384164912539</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC79" t="n">
-        <v>7.788480932295138</v>
+        <v>4.989783431471631</v>
       </c>
     </row>
     <row r="80">
@@ -64541,13 +64541,13 @@
         </is>
       </c>
       <c r="JA80" t="n">
-        <v>0</v>
+        <v>0.3852422535419464</v>
       </c>
       <c r="JB80" t="n">
-        <v>-0.471384164912539</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC80" t="n">
-        <v>7.788481099013347</v>
+        <v>4.989783598189839</v>
       </c>
     </row>
     <row r="81">
@@ -65336,13 +65336,13 @@
         </is>
       </c>
       <c r="JA81" t="n">
-        <v>0</v>
+        <v>0.3608384728431702</v>
       </c>
       <c r="JB81" t="n">
-        <v>-0.471384164912539</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC81" t="n">
-        <v>7.788481296043956</v>
+        <v>4.98978379522045</v>
       </c>
     </row>
     <row r="82">
@@ -66131,13 +66131,13 @@
         </is>
       </c>
       <c r="JA82" t="n">
-        <v>0</v>
+        <v>0.3017500936985016</v>
       </c>
       <c r="JB82" t="n">
-        <v>-0.471384164912539</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC82" t="n">
-        <v>7.788481136903848</v>
+        <v>4.989783636080341</v>
       </c>
     </row>
     <row r="83">
@@ -66926,13 +66926,13 @@
         </is>
       </c>
       <c r="JA83" t="n">
-        <v>0</v>
+        <v>0.372925728559494</v>
       </c>
       <c r="JB83" t="n">
-        <v>-0.471384164912539</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC83" t="n">
-        <v>7.78848117479435</v>
+        <v>4.989783673970843</v>
       </c>
     </row>
     <row r="84">
@@ -67721,13 +67721,13 @@
         </is>
       </c>
       <c r="JA84" t="n">
-        <v>0</v>
+        <v>0.4459499418735504</v>
       </c>
       <c r="JB84" t="n">
-        <v>-0.471384164912539</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC84" t="n">
-        <v>7.788481371824961</v>
+        <v>4.989783871001453</v>
       </c>
     </row>
     <row r="85">
@@ -68516,13 +68516,13 @@
         </is>
       </c>
       <c r="JA85" t="n">
-        <v>0</v>
+        <v>0.3934160172939301</v>
       </c>
       <c r="JB85" t="n">
-        <v>-0.471384164912539</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC85" t="n">
-        <v>7.78848134909066</v>
+        <v>4.989783848267152</v>
       </c>
     </row>
     <row r="86">
@@ -69311,13 +69311,13 @@
         </is>
       </c>
       <c r="JA86" t="n">
-        <v>0</v>
+        <v>0.3418294489383698</v>
       </c>
       <c r="JB86" t="n">
-        <v>-0.471384164912539</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC86" t="n">
-        <v>7.788481197528651</v>
+        <v>4.989783696705144</v>
       </c>
     </row>
     <row r="87">
@@ -70106,13 +70106,13 @@
         </is>
       </c>
       <c r="JA87" t="n">
-        <v>0</v>
+        <v>0.3155956268310547</v>
       </c>
       <c r="JB87" t="n">
-        <v>-0.471384164912539</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC87" t="n">
-        <v>7.788481121747648</v>
+        <v>4.989783620924141</v>
       </c>
     </row>
     <row r="88">
@@ -70901,13 +70901,13 @@
         </is>
       </c>
       <c r="JA88" t="n">
-        <v>0</v>
+        <v>0.36965411901474</v>
       </c>
       <c r="JB88" t="n">
-        <v>-0.471384164912539</v>
+        <v>0.16</v>
       </c>
       <c r="JC88" t="n">
-        <v>7.788481220262952</v>
+        <v>4.989783719439446</v>
       </c>
     </row>
     <row r="89">
@@ -71696,13 +71696,13 @@
         </is>
       </c>
       <c r="JA89" t="n">
-        <v>0</v>
+        <v>0.4673691987991333</v>
       </c>
       <c r="JB89" t="n">
-        <v>-0.471384164912539</v>
+        <v>0.1600000000000001</v>
       </c>
       <c r="JC89" t="n">
-        <v>7.788481227841054</v>
+        <v>4.989783727017546</v>
       </c>
     </row>
     <row r="90">
@@ -72491,13 +72491,13 @@
         </is>
       </c>
       <c r="JA90" t="n">
-        <v>0</v>
+        <v>0.4398794174194336</v>
       </c>
       <c r="JB90" t="n">
-        <v>-0.471384164912539</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC90" t="n">
-        <v>7.788481493074566</v>
+        <v>4.98978399225106</v>
       </c>
     </row>
     <row r="91">
@@ -73286,13 +73286,13 @@
         </is>
       </c>
       <c r="JA91" t="n">
-        <v>0</v>
+        <v>0.3973392248153687</v>
       </c>
       <c r="JB91" t="n">
-        <v>-0.471384164912539</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC91" t="n">
-        <v>7.788481197528651</v>
+        <v>4.989783696705144</v>
       </c>
     </row>
     <row r="92">
@@ -74081,13 +74081,13 @@
         </is>
       </c>
       <c r="JA92" t="n">
-        <v>0</v>
+        <v>0.4647006094455719</v>
       </c>
       <c r="JB92" t="n">
-        <v>-0.471384164912539</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC92" t="n">
-        <v>7.788481440027865</v>
+        <v>4.989783939204357</v>
       </c>
     </row>
     <row r="93">
@@ -74876,13 +74876,13 @@
         </is>
       </c>
       <c r="JA93" t="n">
-        <v>0</v>
+        <v>0.411285936832428</v>
       </c>
       <c r="JB93" t="n">
-        <v>0.5845367972155144</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC93" t="n">
-        <v>7.788481523386968</v>
+        <v>4.989784022563462</v>
       </c>
     </row>
     <row r="94">
@@ -75671,13 +75671,13 @@
         </is>
       </c>
       <c r="JA94" t="n">
-        <v>1</v>
+        <v>0.5563820004463196</v>
       </c>
       <c r="JB94" t="n">
-        <v>0.5845367972155144</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC94" t="n">
-        <v>7.788481356668759</v>
+        <v>4.989783855845253</v>
       </c>
     </row>
     <row r="95">
@@ -76466,13 +76466,13 @@
         </is>
       </c>
       <c r="JA95" t="n">
-        <v>0</v>
+        <v>0.4468315541744232</v>
       </c>
       <c r="JB95" t="n">
-        <v>0.5845367972155144</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC95" t="n">
-        <v>7.788481546121269</v>
+        <v>4.989784045297762</v>
       </c>
     </row>
     <row r="96">
@@ -77261,13 +77261,13 @@
         </is>
       </c>
       <c r="JA96" t="n">
-        <v>0</v>
+        <v>0.4221591055393219</v>
       </c>
       <c r="JB96" t="n">
-        <v>-0.271384164912539</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC96" t="n">
-        <v>7.788481197528651</v>
+        <v>4.989783696705144</v>
       </c>
     </row>
     <row r="97">
@@ -78056,13 +78056,13 @@
         </is>
       </c>
       <c r="JA97" t="n">
-        <v>0</v>
+        <v>0.3697884678840637</v>
       </c>
       <c r="JB97" t="n">
-        <v>-0.271384164912539</v>
+        <v>-0.3</v>
       </c>
       <c r="JC97" t="n">
-        <v>7.788480992919941</v>
+        <v>4.989783492096433</v>
       </c>
     </row>
     <row r="98">
@@ -78851,13 +78851,13 @@
         </is>
       </c>
       <c r="JA98" t="n">
-        <v>0</v>
+        <v>0.3689657151699066</v>
       </c>
       <c r="JB98" t="n">
-        <v>-0.471384164912539</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC98" t="n">
-        <v>7.788481106591447</v>
+        <v>4.989783605767939</v>
       </c>
     </row>
     <row r="99">
@@ -79646,13 +79646,13 @@
         </is>
       </c>
       <c r="JA99" t="n">
-        <v>0</v>
+        <v>0.4123927652835846</v>
       </c>
       <c r="JB99" t="n">
-        <v>-0.471384164912539</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC99" t="n">
-        <v>7.788481121747648</v>
+        <v>4.989783620924141</v>
       </c>
     </row>
     <row r="100">
@@ -80441,13 +80441,13 @@
         </is>
       </c>
       <c r="JA100" t="n">
-        <v>0</v>
+        <v>0.4078432619571686</v>
       </c>
       <c r="JB100" t="n">
-        <v>-0.471384164912539</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC100" t="n">
-        <v>7.788480886826536</v>
+        <v>4.989783386003029</v>
       </c>
     </row>
     <row r="101">
@@ -81236,13 +81236,13 @@
         </is>
       </c>
       <c r="JA101" t="n">
-        <v>0</v>
+        <v>0.3735750615596771</v>
       </c>
       <c r="JB101" t="n">
-        <v>-0.471384164912539</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC101" t="n">
-        <v>7.788480947451339</v>
+        <v>4.989783446627831</v>
       </c>
     </row>
     <row r="102">
@@ -82031,13 +82031,13 @@
         </is>
       </c>
       <c r="JA102" t="n">
-        <v>0</v>
+        <v>0.3374016284942627</v>
       </c>
       <c r="JB102" t="n">
-        <v>-0.471384164912539</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC102" t="n">
-        <v>7.788480818623632</v>
+        <v>4.989783317800124</v>
       </c>
     </row>
     <row r="103">
@@ -82826,13 +82826,13 @@
         </is>
       </c>
       <c r="JA103" t="n">
-        <v>0</v>
+        <v>0.4744328260421753</v>
       </c>
       <c r="JB103" t="n">
-        <v>-0.471384164912539</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC103" t="n">
-        <v>7.788480955029439</v>
+        <v>4.989783454205933</v>
       </c>
     </row>
     <row r="104">
@@ -83621,13 +83621,13 @@
         </is>
       </c>
       <c r="JA104" t="n">
-        <v>0</v>
+        <v>0.3993621468544006</v>
       </c>
       <c r="JB104" t="n">
-        <v>-0.471384164912539</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC104" t="n">
-        <v>7.788481129325747</v>
+        <v>4.989783628502241</v>
       </c>
     </row>
     <row r="105">
@@ -84416,13 +84416,13 @@
         </is>
       </c>
       <c r="JA105" t="n">
-        <v>0</v>
+        <v>0.3889554440975189</v>
       </c>
       <c r="JB105" t="n">
-        <v>-0.471384164912539</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC105" t="n">
-        <v>7.788481273309656</v>
+        <v>4.989783772486148</v>
       </c>
     </row>
     <row r="106">
@@ -85211,13 +85211,13 @@
         </is>
       </c>
       <c r="JA106" t="n">
-        <v>0</v>
+        <v>0.417988508939743</v>
       </c>
       <c r="JB106" t="n">
-        <v>-0.471384164912539</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC106" t="n">
-        <v>7.788481106591447</v>
+        <v>4.989783605767939</v>
       </c>
     </row>
     <row r="107">
@@ -86006,13 +86006,13 @@
         </is>
       </c>
       <c r="JA107" t="n">
-        <v>0</v>
+        <v>0.4165776073932648</v>
       </c>
       <c r="JB107" t="n">
-        <v>-0.471384164912539</v>
+        <v>0.3</v>
       </c>
       <c r="JC107" t="n">
-        <v>7.788481099013347</v>
+        <v>4.989783598189839</v>
       </c>
     </row>
     <row r="108">
@@ -86801,13 +86801,13 @@
         </is>
       </c>
       <c r="JA108" t="n">
-        <v>0</v>
+        <v>0.3515588939189911</v>
       </c>
       <c r="JB108" t="n">
-        <v>-0.471384164912539</v>
+        <v>0.16</v>
       </c>
       <c r="JC108" t="n">
-        <v>7.788480811045531</v>
+        <v>4.989783310222024</v>
       </c>
     </row>
     <row r="109">
@@ -87596,13 +87596,13 @@
         </is>
       </c>
       <c r="JA109" t="n">
-        <v>0</v>
+        <v>0.3659402430057526</v>
       </c>
       <c r="JB109" t="n">
-        <v>-0.471384164912539</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC109" t="n">
-        <v>7.788480826201732</v>
+        <v>4.989783325378225</v>
       </c>
     </row>
     <row r="110">
@@ -88391,13 +88391,13 @@
         </is>
       </c>
       <c r="JA110" t="n">
-        <v>0</v>
+        <v>0.3550622761249542</v>
       </c>
       <c r="JB110" t="n">
-        <v>-0.471384164912539</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC110" t="n">
-        <v>7.788481053544745</v>
+        <v>4.989783552721237</v>
       </c>
     </row>
     <row r="111">
@@ -89186,13 +89186,13 @@
         </is>
       </c>
       <c r="JA111" t="n">
-        <v>0</v>
+        <v>0.3898627161979675</v>
       </c>
       <c r="JB111" t="n">
-        <v>-0.471384164912539</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC111" t="n">
-        <v>7.788481038388543</v>
+        <v>4.989783537565036</v>
       </c>
     </row>
     <row r="112">
@@ -89981,13 +89981,13 @@
         </is>
       </c>
       <c r="JA112" t="n">
-        <v>0</v>
+        <v>0.3581028580665588</v>
       </c>
       <c r="JB112" t="n">
-        <v>-0.471384164912539</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC112" t="n">
-        <v>7.78848114448195</v>
+        <v>4.989783643658441</v>
       </c>
     </row>
     <row r="113">
@@ -90776,13 +90776,13 @@
         </is>
       </c>
       <c r="JA113" t="n">
-        <v>0</v>
+        <v>0.3484627902507782</v>
       </c>
       <c r="JB113" t="n">
-        <v>-0.471384164912539</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC113" t="n">
-        <v>7.788480871670334</v>
+        <v>4.989783370846827</v>
       </c>
     </row>
     <row r="114">
@@ -91571,13 +91571,13 @@
         </is>
       </c>
       <c r="JA114" t="n">
-        <v>0</v>
+        <v>0.394222766160965</v>
       </c>
       <c r="JB114" t="n">
-        <v>-0.471384164912539</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC114" t="n">
-        <v>7.788480970185639</v>
+        <v>4.989783469362132</v>
       </c>
     </row>
     <row r="115">
@@ -92366,13 +92366,13 @@
         </is>
       </c>
       <c r="JA115" t="n">
-        <v>0</v>
+        <v>0.3771649897098541</v>
       </c>
       <c r="JB115" t="n">
-        <v>-0.471384164912539</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC115" t="n">
-        <v>7.788481121747648</v>
+        <v>4.989783620924141</v>
       </c>
     </row>
     <row r="116">
@@ -93161,13 +93161,13 @@
         </is>
       </c>
       <c r="JA116" t="n">
-        <v>0</v>
+        <v>0.3700193762779236</v>
       </c>
       <c r="JB116" t="n">
-        <v>-0.471384164912539</v>
+        <v>0.16</v>
       </c>
       <c r="JC116" t="n">
-        <v>7.788481136903848</v>
+        <v>4.989783636080341</v>
       </c>
     </row>
     <row r="117">
@@ -93956,13 +93956,13 @@
         </is>
       </c>
       <c r="JA117" t="n">
-        <v>0</v>
+        <v>0.4057582020759583</v>
       </c>
       <c r="JB117" t="n">
-        <v>-0.471384164912539</v>
+        <v>0.16</v>
       </c>
       <c r="JC117" t="n">
-        <v>7.788481114169548</v>
+        <v>4.98978361334604</v>
       </c>
     </row>
     <row r="118">
@@ -94751,13 +94751,13 @@
         </is>
       </c>
       <c r="JA118" t="n">
-        <v>0</v>
+        <v>0.438564270734787</v>
       </c>
       <c r="JB118" t="n">
-        <v>-0.471384164912539</v>
+        <v>0.1600000000000001</v>
       </c>
       <c r="JC118" t="n">
-        <v>7.788481197528651</v>
+        <v>4.989783696705144</v>
       </c>
     </row>
     <row r="119">
@@ -95546,13 +95546,13 @@
         </is>
       </c>
       <c r="JA119" t="n">
-        <v>0</v>
+        <v>0.4037221074104309</v>
       </c>
       <c r="JB119" t="n">
-        <v>-0.471384164912539</v>
+        <v>0.3</v>
       </c>
       <c r="JC119" t="n">
-        <v>7.788481296043956</v>
+        <v>4.98978379522045</v>
       </c>
     </row>
     <row r="120">
@@ -96341,13 +96341,13 @@
         </is>
       </c>
       <c r="JA120" t="n">
-        <v>0</v>
+        <v>0.3877699077129364</v>
       </c>
       <c r="JB120" t="n">
-        <v>-0.471384164912539</v>
+        <v>0.3</v>
       </c>
       <c r="JC120" t="n">
-        <v>7.788481129325747</v>
+        <v>4.989783628502241</v>
       </c>
     </row>
     <row r="121">
@@ -97136,13 +97136,13 @@
         </is>
       </c>
       <c r="JA121" t="n">
-        <v>0</v>
+        <v>0.3994781970977783</v>
       </c>
       <c r="JB121" t="n">
-        <v>-0.471384164912539</v>
+        <v>0.16</v>
       </c>
       <c r="JC121" t="n">
-        <v>7.788481114169548</v>
+        <v>4.98978361334604</v>
       </c>
     </row>
     <row r="122">
@@ -97931,13 +97931,13 @@
         </is>
       </c>
       <c r="JA122" t="n">
-        <v>0</v>
+        <v>0.4014085233211517</v>
       </c>
       <c r="JB122" t="n">
-        <v>-0.471384164912539</v>
+        <v>0.02000000000000007</v>
       </c>
       <c r="JC122" t="n">
-        <v>7.788481083857145</v>
+        <v>4.989783583033638</v>
       </c>
     </row>
     <row r="123">
@@ -98726,13 +98726,13 @@
         </is>
       </c>
       <c r="JA123" t="n">
-        <v>0</v>
+        <v>0.3974135220050812</v>
       </c>
       <c r="JB123" t="n">
-        <v>-0.471384164912539</v>
+        <v>0.16</v>
       </c>
       <c r="JC123" t="n">
-        <v>7.788481068700945</v>
+        <v>4.989783567877438</v>
       </c>
     </row>
     <row r="124">
@@ -99521,13 +99521,13 @@
         </is>
       </c>
       <c r="JA124" t="n">
-        <v>0</v>
+        <v>0.3742357492446899</v>
       </c>
       <c r="JB124" t="n">
-        <v>-0.471384164912539</v>
+        <v>-0.3</v>
       </c>
       <c r="JC124" t="n">
-        <v>7.788481106591447</v>
+        <v>4.989783605767939</v>
       </c>
     </row>
     <row r="125">
@@ -100316,13 +100316,13 @@
         </is>
       </c>
       <c r="JA125" t="n">
-        <v>0</v>
+        <v>0.3907568156719208</v>
       </c>
       <c r="JB125" t="n">
-        <v>-0.471384164912539</v>
+        <v>0.4400000000000002</v>
       </c>
       <c r="JC125" t="n">
-        <v>7.788481121747648</v>
+        <v>4.989783620924141</v>
       </c>
     </row>
     <row r="126">
@@ -101111,13 +101111,13 @@
         </is>
       </c>
       <c r="JA126" t="n">
-        <v>0</v>
+        <v>0.4416378438472748</v>
       </c>
       <c r="JB126" t="n">
-        <v>-0.471384164912539</v>
+        <v>0.5800000000000002</v>
       </c>
       <c r="JC126" t="n">
-        <v>7.788481114169548</v>
+        <v>4.98978361334604</v>
       </c>
     </row>
   </sheetData>

--- a/out/MLP-S4_repeat_2_000007.xlsx
+++ b/out/MLP-S4_repeat_2_000007.xlsx
@@ -46259,7 +46259,7 @@
         <v>0.3504213690757751</v>
       </c>
       <c r="JB57" t="n">
-        <v>0.16</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC57" t="n">
         <v>4.98981186073719</v>
@@ -47054,7 +47054,7 @@
         <v>0.6651333570480347</v>
       </c>
       <c r="JB58" t="n">
-        <v>0.1600000000000001</v>
+        <v>0.02000000000000007</v>
       </c>
       <c r="JC58" t="n">
         <v>4.989803676537635</v>
@@ -47849,7 +47849,7 @@
         <v>0.5251737236976624</v>
       </c>
       <c r="JB59" t="n">
-        <v>0.1600000000000001</v>
+        <v>0.02000000000000007</v>
       </c>
       <c r="JC59" t="n">
         <v>4.989813216435479</v>
@@ -48644,7 +48644,7 @@
         <v>0.3761074542999268</v>
       </c>
       <c r="JB60" t="n">
-        <v>0.16</v>
+        <v>0.02000000000000007</v>
       </c>
       <c r="JC60" t="n">
         <v>4.989805242565942</v>
@@ -49439,7 +49439,7 @@
         <v>0.3653608858585358</v>
       </c>
       <c r="JB61" t="n">
-        <v>-0.1199999999999999</v>
+        <v>-0.2599999999999998</v>
       </c>
       <c r="JC61" t="n">
         <v>4.989798461775472</v>
